--- a/data/data_shichigawahama_w1.xlsx
+++ b/data/data_shichigawahama_w1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC678579-AE9D-4303-B0CA-7093701FE809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33879256-A346-4A1C-91A5-118F544C697B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="499">
   <si>
     <t>name</t>
     <phoneticPr fontId="2"/>
@@ -1672,6 +1672,10 @@
   </si>
   <si>
     <t>wave1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>id</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2006,350 +2010,386 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N231"/>
+  <dimension ref="A1:O231"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.4140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.4140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>497</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>485</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>486</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>487</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>488</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>489</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>490</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>491</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>492</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>493</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>494</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>495</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2">
         <v>120</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>5</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>6</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>6</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>6</v>
       </c>
       <c r="J4" t="s">
         <v>6</v>
       </c>
-      <c r="N4" t="s">
+      <c r="K4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="N6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
+      <c r="O6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7">
+      <c r="F7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7">
         <v>50</v>
       </c>
-      <c r="H7" t="s">
-        <v>10</v>
-      </c>
-      <c r="N7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="O8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>0</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" t="s">
-        <v>10</v>
-      </c>
-      <c r="N10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
+      </c>
+      <c r="O10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>30</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
         <v>5</v>
       </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
       <c r="J11" t="s">
         <v>31</v>
       </c>
       <c r="K11" t="s">
         <v>31</v>
       </c>
-      <c r="M11" t="s">
+      <c r="L11" t="s">
         <v>31</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>0</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
+    <row r="13" spans="1:15">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>35</v>
       </c>
-      <c r="E13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13">
+      <c r="F13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13">
         <v>100</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>36</v>
-      </c>
-      <c r="I13" t="s">
-        <v>6</v>
       </c>
       <c r="J13" t="s">
         <v>6</v>
@@ -2357,189 +2397,213 @@
       <c r="K13" t="s">
         <v>6</v>
       </c>
-      <c r="M13" t="s">
+      <c r="L13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
+      <c r="N13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>38</v>
       </c>
-      <c r="E14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>30</v>
+      <c r="F14" t="s">
+        <v>4</v>
       </c>
       <c r="G14">
         <v>30</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14">
+        <v>30</v>
+      </c>
+      <c r="I14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>40</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
+    <row r="16" spans="1:15">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
         <v>23</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>42</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>13</v>
       </c>
-      <c r="N16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
+      <c r="O16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
         <v>23</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>44</v>
       </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" t="s">
-        <v>10</v>
-      </c>
-      <c r="N17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
         <v>46</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>47</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>13</v>
       </c>
-      <c r="N18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
+      <c r="O18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
         <v>23</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>49</v>
       </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" t="s">
-        <v>10</v>
-      </c>
-      <c r="N19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" t="s">
+        <v>10</v>
+      </c>
+      <c r="O19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>51</v>
       </c>
-      <c r="E20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20">
+      <c r="F20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20">
         <v>23</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>5</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>6</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
+    <row r="21" spans="1:15">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
         <v>52</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
         <v>23</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>53</v>
       </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="F21" t="s">
         <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J21" t="s">
         <v>6</v>
@@ -2547,246 +2611,279 @@
       <c r="K21" t="s">
         <v>6</v>
       </c>
-      <c r="M21" t="s">
+      <c r="L21" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" t="s">
+      <c r="N21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>0</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>46</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
+    <row r="23" spans="1:15">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>56</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
         <v>46</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>57</v>
       </c>
-      <c r="E23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23">
+      <c r="F23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23">
         <v>30</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
-      <c r="A24" t="s">
+    <row r="24" spans="1:15">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>58</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
         <v>46</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>59</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="N24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" t="s">
+      <c r="O24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
         <v>60</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
         <v>23</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>61</v>
       </c>
-      <c r="E25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25">
+      <c r="F25" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25">
         <v>100</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
-      <c r="A26" t="s">
+    <row r="26" spans="1:15">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
         <v>62</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>23</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>63</v>
       </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="F26" t="s">
         <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J26" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" t="s">
+      <c r="K26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
         <v>23</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>65</v>
       </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="F27" t="s">
         <v>10</v>
       </c>
       <c r="I27" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J27" t="s">
         <v>31</v>
       </c>
-      <c r="M27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" t="s">
+      <c r="K27" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>66</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>0</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>46</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
-      <c r="A29" t="s">
+    <row r="29" spans="1:15">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
         <v>46</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>69</v>
       </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29">
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
         <v>15</v>
       </c>
-      <c r="H29" t="s">
-        <v>10</v>
-      </c>
-      <c r="N29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" t="s">
+      <c r="I29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
         <v>70</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>0</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>23</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
-      <c r="A31" t="s">
+    <row r="31" spans="1:15">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
         <v>23</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>73</v>
       </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" t="s">
         <v>36</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>6</v>
       </c>
-      <c r="N31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" t="s">
+      <c r="O31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
         <v>74</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
         <v>23</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>75</v>
       </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="F32" t="s">
         <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32" t="s">
         <v>6</v>
@@ -2794,152 +2891,170 @@
       <c r="K32" t="s">
         <v>6</v>
       </c>
-      <c r="M32" t="s">
+      <c r="L32" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" t="s">
+      <c r="N32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
         <v>76</v>
       </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
         <v>23</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>77</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
-      <c r="A34" t="s">
+    <row r="34" spans="1:15">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
         <v>78</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
         <v>23</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>79</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>13</v>
       </c>
-      <c r="N34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" t="s">
+      <c r="O34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>80</v>
       </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
         <v>23</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>81</v>
       </c>
-      <c r="E35" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="F35" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" t="s">
         <v>36</v>
       </c>
-      <c r="I35" t="s">
-        <v>31</v>
-      </c>
       <c r="J35" t="s">
         <v>31</v>
       </c>
       <c r="K35" t="s">
         <v>31</v>
       </c>
-      <c r="M35" t="s">
+      <c r="L35" t="s">
         <v>31</v>
       </c>
       <c r="N35" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
-      <c r="A36" t="s">
+    <row r="36" spans="1:15">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
         <v>82</v>
       </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
         <v>23</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>83</v>
       </c>
-      <c r="E36" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36">
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36">
         <v>70</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
-      <c r="A37" t="s">
+    <row r="37" spans="1:15">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
         <v>84</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
         <v>23</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>85</v>
       </c>
-      <c r="E37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37">
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37">
         <v>200</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
-      <c r="A38" t="s">
+    <row r="38" spans="1:15">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
         <v>86</v>
       </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
         <v>23</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>87</v>
       </c>
-      <c r="E38" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38">
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38">
         <v>40</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>5</v>
-      </c>
-      <c r="I38" t="s">
-        <v>6</v>
       </c>
       <c r="J38" t="s">
         <v>6</v>
@@ -2947,165 +3062,189 @@
       <c r="K38" t="s">
         <v>6</v>
       </c>
-      <c r="M38" t="s">
+      <c r="L38" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" t="s">
+      <c r="N38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
         <v>88</v>
       </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
         <v>46</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>89</v>
       </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H39" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" t="s">
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
         <v>90</v>
       </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
         <v>23</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>91</v>
       </c>
-      <c r="E40" t="s">
-        <v>4</v>
-      </c>
-      <c r="F40">
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40">
         <v>45</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
-      <c r="A41" t="s">
+    <row r="41" spans="1:15">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
         <v>92</v>
       </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
         <v>23</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>93</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
-      <c r="A42" t="s">
+    <row r="42" spans="1:15">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
         <v>94</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>0</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>46</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
-      <c r="A43" t="s">
+    <row r="43" spans="1:15">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
         <v>96</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>0</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>46</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
-      <c r="A44" t="s">
+    <row r="44" spans="1:15">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
         <v>98</v>
       </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
         <v>46</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>99</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>13</v>
       </c>
-      <c r="N44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" t="s">
+      <c r="O44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
         <v>100</v>
       </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
         <v>23</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>101</v>
       </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="H45" t="s">
-        <v>10</v>
-      </c>
-      <c r="N45" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" t="s">
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" t="s">
+        <v>10</v>
+      </c>
+      <c r="O45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
         <v>102</v>
       </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
         <v>23</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>103</v>
       </c>
-      <c r="E46" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46">
+      <c r="F46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46">
         <v>220</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>36</v>
-      </c>
-      <c r="I46" t="s">
-        <v>6</v>
       </c>
       <c r="J46" t="s">
         <v>6</v>
@@ -3113,478 +3252,544 @@
       <c r="K46" t="s">
         <v>6</v>
       </c>
-      <c r="M46" t="s">
+      <c r="L46" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" t="s">
+      <c r="N46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
         <v>104</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>0</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>46</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
-      <c r="A48" t="s">
+    <row r="48" spans="1:15">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
         <v>106</v>
       </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
         <v>46</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>107</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
-      <c r="A49" t="s">
+    <row r="49" spans="1:15">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
         <v>108</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
         <v>23</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>109</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
-      <c r="A50" t="s">
+    <row r="50" spans="1:15">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
         <v>110</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>0</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>23</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
-      <c r="A51" t="s">
+    <row r="51" spans="1:15">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
         <v>112</v>
       </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
         <v>113</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>114</v>
       </c>
-      <c r="E51" t="s">
-        <v>4</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" t="s">
         <v>5</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>6</v>
       </c>
-      <c r="L51" t="s">
+      <c r="M51" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
-      <c r="A52" t="s">
+    <row r="52" spans="1:15">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
         <v>115</v>
       </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
         <v>113</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>116</v>
       </c>
-      <c r="E52" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
-      <c r="A53" t="s">
+    <row r="53" spans="1:15">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
         <v>117</v>
       </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
         <v>113</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>118</v>
       </c>
-      <c r="E53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F53">
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53">
         <v>82</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>36</v>
       </c>
-      <c r="I53" t="s">
-        <v>31</v>
-      </c>
       <c r="J53" t="s">
         <v>31</v>
       </c>
       <c r="K53" t="s">
         <v>31</v>
       </c>
-      <c r="M53" t="s">
+      <c r="L53" t="s">
         <v>31</v>
       </c>
       <c r="N53" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" t="s">
+        <v>31</v>
+      </c>
+      <c r="O53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
         <v>474</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>0</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>119</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
-      <c r="A55" t="s">
+    <row r="55" spans="1:15">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
         <v>121</v>
       </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
         <v>119</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>122</v>
       </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="H55" t="s">
-        <v>10</v>
-      </c>
-      <c r="N55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" t="s">
+      <c r="F55" t="s">
+        <v>10</v>
+      </c>
+      <c r="I55" t="s">
+        <v>10</v>
+      </c>
+      <c r="O55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
         <v>123</v>
       </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
         <v>119</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>124</v>
       </c>
-      <c r="E56" t="s">
-        <v>4</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="I56" t="s">
         <v>5</v>
       </c>
-      <c r="J56" t="s">
-        <v>31</v>
-      </c>
-      <c r="N56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" t="s">
+      <c r="K56" t="s">
+        <v>31</v>
+      </c>
+      <c r="O56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
         <v>125</v>
       </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
         <v>113</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>126</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>13</v>
       </c>
-      <c r="I57" t="s">
-        <v>31</v>
-      </c>
       <c r="J57" t="s">
         <v>31</v>
       </c>
-      <c r="L57" t="s">
-        <v>31</v>
-      </c>
-      <c r="N57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" t="s">
+      <c r="K57" t="s">
+        <v>31</v>
+      </c>
+      <c r="M57" t="s">
+        <v>31</v>
+      </c>
+      <c r="O57" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
         <v>475</v>
       </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
         <v>119</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>127</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>13</v>
       </c>
-      <c r="N58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" t="s">
+      <c r="O58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
         <v>128</v>
       </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="s">
         <v>119</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>476</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
-      <c r="A60" t="s">
+    <row r="60" spans="1:15">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
         <v>129</v>
       </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
         <v>113</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>130</v>
       </c>
-      <c r="E60" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60">
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60">
         <v>30</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
         <v>5</v>
       </c>
-      <c r="N60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" t="s">
+      <c r="O60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
         <v>131</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>0</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>113</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
-      <c r="A62" t="s">
+    <row r="62" spans="1:15">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
         <v>133</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>0</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>113</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
-      <c r="A63" t="s">
+    <row r="63" spans="1:15">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
         <v>135</v>
       </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
         <v>113</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>136</v>
       </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="H63" t="s">
-        <v>10</v>
-      </c>
-      <c r="N63" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" t="s">
+      <c r="F63" t="s">
+        <v>10</v>
+      </c>
+      <c r="I63" t="s">
+        <v>10</v>
+      </c>
+      <c r="O63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
         <v>137</v>
       </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
         <v>113</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>138</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>13</v>
       </c>
-      <c r="N64" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" t="s">
+      <c r="O64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
         <v>139</v>
       </c>
-      <c r="B65">
-        <v>1</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65" t="s">
         <v>113</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>140</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>13</v>
       </c>
-      <c r="N65" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
-      <c r="A66" t="s">
+      <c r="O65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
         <v>141</v>
       </c>
-      <c r="B66">
-        <v>1</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
         <v>119</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>142</v>
       </c>
-      <c r="E66" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66">
+      <c r="F66" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66">
         <v>34</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>3</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
         <v>36</v>
       </c>
-      <c r="I66" t="s">
-        <v>31</v>
-      </c>
       <c r="J66" t="s">
         <v>31</v>
       </c>
       <c r="K66" t="s">
         <v>31</v>
       </c>
-      <c r="M66" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
-      <c r="A67" t="s">
+      <c r="L66" t="s">
+        <v>31</v>
+      </c>
+      <c r="N66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
         <v>143</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>0</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>113</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
-      <c r="A68" t="s">
+    <row r="68" spans="1:15">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
         <v>145</v>
       </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="s">
         <v>113</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>146</v>
       </c>
-      <c r="E68" t="s">
-        <v>4</v>
-      </c>
-      <c r="G68">
+      <c r="F68" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68">
         <v>28</v>
       </c>
-      <c r="H68" t="s">
-        <v>10</v>
-      </c>
       <c r="I68" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J68" t="s">
         <v>31</v>
@@ -3592,436 +3797,493 @@
       <c r="K68" t="s">
         <v>31</v>
       </c>
-      <c r="N68" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
-      <c r="A69" t="s">
+      <c r="L68" t="s">
+        <v>31</v>
+      </c>
+      <c r="O68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
         <v>147</v>
       </c>
-      <c r="B69">
-        <v>1</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
         <v>113</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>148</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>13</v>
       </c>
-      <c r="N69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" t="s">
+      <c r="O69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
         <v>149</v>
       </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
         <v>113</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>150</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>13</v>
       </c>
-      <c r="N70" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
-      <c r="A71" t="s">
+      <c r="O70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
         <v>151</v>
       </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="s">
         <v>113</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>152</v>
       </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="H71" t="s">
+      <c r="F71" t="s">
         <v>10</v>
       </c>
       <c r="I71" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J71" t="s">
         <v>6</v>
       </c>
-      <c r="L71" t="s">
+      <c r="K71" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="A72" t="s">
+      <c r="M71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
         <v>153</v>
       </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
         <v>113</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>154</v>
       </c>
-      <c r="E72" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72">
+      <c r="F72" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72">
         <v>35</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>7</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
         <v>5</v>
       </c>
-      <c r="J72" t="s">
-        <v>31</v>
-      </c>
-      <c r="L72" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
-      <c r="A73" t="s">
+      <c r="K72" t="s">
+        <v>31</v>
+      </c>
+      <c r="M72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
         <v>155</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>0</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>113</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
-      <c r="A74" t="s">
+    <row r="74" spans="1:15">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
         <v>157</v>
       </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
         <v>113</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>158</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>13</v>
       </c>
-      <c r="N74" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
-      <c r="A75" t="s">
+      <c r="O74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
         <v>159</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>0</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>113</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
-      <c r="A76" t="s">
+    <row r="76" spans="1:15">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
         <v>161</v>
       </c>
-      <c r="B76">
+      <c r="C76">
         <v>0</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>113</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
-      <c r="A77" t="s">
+    <row r="77" spans="1:15">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
         <v>163</v>
       </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
         <v>113</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>164</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>13</v>
       </c>
-      <c r="I77" t="s">
-        <v>31</v>
-      </c>
-      <c r="N77" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
-      <c r="A78" t="s">
+      <c r="J77" t="s">
+        <v>31</v>
+      </c>
+      <c r="O77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
         <v>165</v>
       </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78" t="s">
         <v>113</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>166</v>
       </c>
-      <c r="E78" t="s">
-        <v>4</v>
-      </c>
-      <c r="F78">
+      <c r="F78" t="s">
+        <v>4</v>
+      </c>
+      <c r="G78">
         <v>140</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>15</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>36</v>
       </c>
-      <c r="I78" t="s">
-        <v>31</v>
-      </c>
       <c r="J78" t="s">
         <v>31</v>
       </c>
       <c r="K78" t="s">
         <v>31</v>
       </c>
-      <c r="M78" t="s">
+      <c r="L78" t="s">
         <v>31</v>
       </c>
       <c r="N78" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
-      <c r="A79" t="s">
+        <v>31</v>
+      </c>
+      <c r="O78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
         <v>167</v>
       </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
         <v>113</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>168</v>
       </c>
-      <c r="E79" t="s">
-        <v>4</v>
-      </c>
-      <c r="F79">
+      <c r="F79" t="s">
+        <v>4</v>
+      </c>
+      <c r="G79">
         <v>6</v>
       </c>
-      <c r="H79" t="s">
-        <v>10</v>
-      </c>
-      <c r="N79" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
-      <c r="A80" t="s">
+      <c r="I79" t="s">
+        <v>10</v>
+      </c>
+      <c r="O79" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
         <v>169</v>
       </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
         <v>113</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>170</v>
       </c>
-      <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="H80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
-      <c r="A81" t="s">
+      <c r="F80" t="s">
+        <v>10</v>
+      </c>
+      <c r="I80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
         <v>171</v>
       </c>
-      <c r="B81">
+      <c r="C81">
         <v>0</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>113</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
-      <c r="A82" t="s">
+    <row r="82" spans="1:15">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
         <v>173</v>
       </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
         <v>113</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>174</v>
       </c>
-      <c r="E82" t="s">
-        <v>4</v>
-      </c>
-      <c r="F82">
+      <c r="F82" t="s">
+        <v>4</v>
+      </c>
+      <c r="G82">
         <v>35</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>36</v>
       </c>
-      <c r="J82" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
-      <c r="A83" t="s">
+      <c r="K82" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
         <v>175</v>
       </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="s">
         <v>113</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>176</v>
       </c>
-      <c r="E83" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" t="s">
+      <c r="F83" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
-      <c r="A84" t="s">
+    <row r="84" spans="1:15">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
         <v>177</v>
       </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
         <v>119</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>178</v>
       </c>
-      <c r="E84" t="s">
-        <v>4</v>
-      </c>
-      <c r="F84">
+      <c r="F84" t="s">
+        <v>4</v>
+      </c>
+      <c r="G84">
         <v>11</v>
       </c>
-      <c r="H84" t="s">
-        <v>10</v>
-      </c>
-      <c r="N84" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="A85" t="s">
+      <c r="I84" t="s">
+        <v>10</v>
+      </c>
+      <c r="O84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
         <v>179</v>
       </c>
-      <c r="B85">
-        <v>1</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85" t="s">
         <v>119</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>180</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>13</v>
       </c>
-      <c r="N85" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
-      <c r="A86" t="s">
+      <c r="O85" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
         <v>181</v>
       </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
         <v>119</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>178</v>
       </c>
-      <c r="E86" t="s">
-        <v>4</v>
-      </c>
-      <c r="F86">
+      <c r="F86" t="s">
+        <v>4</v>
+      </c>
+      <c r="G86">
         <v>9</v>
       </c>
-      <c r="H86" t="s">
-        <v>10</v>
-      </c>
-      <c r="N86" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
-      <c r="A87" t="s">
+      <c r="I86" t="s">
+        <v>10</v>
+      </c>
+      <c r="O86" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
         <v>182</v>
       </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
         <v>113</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>183</v>
       </c>
-      <c r="E87" t="s">
-        <v>4</v>
-      </c>
-      <c r="H87" t="s">
-        <v>10</v>
+      <c r="F87" t="s">
+        <v>4</v>
       </c>
       <c r="I87" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J87" t="s">
         <v>31</v>
@@ -4033,59 +4295,65 @@
         <v>31</v>
       </c>
       <c r="M87" t="s">
+        <v>31</v>
+      </c>
+      <c r="N87" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
-      <c r="A88" t="s">
+    <row r="88" spans="1:15">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
         <v>184</v>
       </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
         <v>113</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>185</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>13</v>
       </c>
-      <c r="I88" t="s">
-        <v>31</v>
-      </c>
       <c r="J88" t="s">
         <v>31</v>
       </c>
-      <c r="L88" t="s">
-        <v>31</v>
-      </c>
-      <c r="N88" t="s">
+      <c r="K88" t="s">
+        <v>31</v>
+      </c>
+      <c r="M88" t="s">
+        <v>31</v>
+      </c>
+      <c r="O88" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
-      <c r="A89" t="s">
+    <row r="89" spans="1:15">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
         <v>186</v>
       </c>
-      <c r="B89">
-        <v>1</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
         <v>113</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>187</v>
       </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="H89" t="s">
+      <c r="F89" t="s">
         <v>10</v>
       </c>
       <c r="I89" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J89" t="s">
         <v>31</v>
@@ -4093,126 +4361,141 @@
       <c r="K89" t="s">
         <v>31</v>
       </c>
-      <c r="M89" t="s">
+      <c r="L89" t="s">
         <v>31</v>
       </c>
       <c r="N89" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14">
-      <c r="A90" t="s">
+        <v>31</v>
+      </c>
+      <c r="O89" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
         <v>188</v>
       </c>
-      <c r="B90">
+      <c r="C90">
         <v>0</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>113</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
-      <c r="A91" t="s">
+    <row r="91" spans="1:15">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
         <v>190</v>
       </c>
-      <c r="B91">
-        <v>1</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
         <v>113</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>191</v>
       </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="H91" t="s">
+      <c r="F91" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" t="s">
         <v>36</v>
       </c>
-      <c r="I91" t="s">
-        <v>31</v>
-      </c>
       <c r="J91" t="s">
         <v>31</v>
       </c>
-      <c r="L91" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
-      <c r="A92" t="s">
+      <c r="K91" t="s">
+        <v>31</v>
+      </c>
+      <c r="M91" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
         <v>192</v>
       </c>
-      <c r="B92">
-        <v>1</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
         <v>113</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>193</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>13</v>
       </c>
-      <c r="N92" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
-      <c r="A93" t="s">
+      <c r="O92" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
         <v>194</v>
       </c>
-      <c r="B93">
-        <v>1</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
         <v>119</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>195</v>
       </c>
-      <c r="E93" t="s">
-        <v>4</v>
-      </c>
-      <c r="F93">
+      <c r="F93" t="s">
+        <v>4</v>
+      </c>
+      <c r="G93">
         <v>43</v>
       </c>
-      <c r="H93" t="s">
+      <c r="I93" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
-      <c r="A94" t="s">
+    <row r="94" spans="1:15">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
         <v>196</v>
       </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94" t="s">
         <v>113</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>197</v>
       </c>
-      <c r="E94" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94">
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94">
         <v>30</v>
       </c>
-      <c r="G94">
-        <v>10</v>
-      </c>
-      <c r="H94" t="s">
+      <c r="H94">
         <v>10</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J94" t="s">
         <v>31</v>
@@ -4223,321 +4506,372 @@
       <c r="L94" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="95" spans="1:14">
-      <c r="A95" t="s">
+      <c r="M94" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
         <v>198</v>
       </c>
-      <c r="B95">
-        <v>1</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
         <v>113</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>199</v>
       </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="H95" t="s">
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="I95" t="s">
         <v>36</v>
       </c>
-      <c r="I95" t="s">
-        <v>31</v>
-      </c>
       <c r="J95" t="s">
         <v>31</v>
       </c>
-      <c r="M95" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14">
-      <c r="A96" t="s">
+      <c r="K95" t="s">
+        <v>31</v>
+      </c>
+      <c r="N95" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
         <v>200</v>
       </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96" t="s">
         <v>113</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>201</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
-      <c r="A97" t="s">
+    <row r="97" spans="1:15">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
         <v>202</v>
       </c>
-      <c r="B97">
+      <c r="C97">
         <v>0</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>113</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
-      <c r="A98" t="s">
+    <row r="98" spans="1:15">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
         <v>204</v>
       </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
         <v>113</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>205</v>
       </c>
-      <c r="E98" t="s">
-        <v>4</v>
-      </c>
-      <c r="F98">
+      <c r="F98" t="s">
+        <v>4</v>
+      </c>
+      <c r="G98">
         <v>115</v>
       </c>
-      <c r="H98" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
-      <c r="A99" t="s">
+      <c r="I98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
         <v>206</v>
       </c>
-      <c r="B99">
-        <v>1</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
         <v>113</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>207</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>13</v>
       </c>
-      <c r="N99" t="s">
+      <c r="O99" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
-      <c r="A100" t="s">
+    <row r="100" spans="1:15">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
         <v>208</v>
       </c>
-      <c r="B100">
+      <c r="C100">
         <v>0</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>119</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
-      <c r="A101" t="s">
+    <row r="101" spans="1:15">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
         <v>210</v>
       </c>
-      <c r="B101">
-        <v>1</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
         <v>211</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>212</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>13</v>
       </c>
-      <c r="I101" t="s">
-        <v>31</v>
-      </c>
       <c r="J101" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="102" spans="1:14">
-      <c r="A102" t="s">
+      <c r="K101" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
         <v>477</v>
       </c>
-      <c r="B102">
+      <c r="C102">
         <v>0</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>213</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
-      <c r="A103" t="s">
+    <row r="103" spans="1:15">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
         <v>215</v>
       </c>
-      <c r="B103">
+      <c r="C103">
         <v>0</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>211</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
-      <c r="A104" t="s">
+    <row r="104" spans="1:15">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
         <v>217</v>
       </c>
-      <c r="B104">
+      <c r="C104">
         <v>0</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>213</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
-      <c r="A105" t="s">
+    <row r="105" spans="1:15">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
         <v>219</v>
       </c>
-      <c r="B105">
-        <v>1</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
         <v>211</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>220</v>
       </c>
-      <c r="E105" t="s">
-        <v>4</v>
-      </c>
-      <c r="F105">
+      <c r="F105" t="s">
+        <v>4</v>
+      </c>
+      <c r="G105">
         <v>50</v>
       </c>
-      <c r="H105" t="s">
+      <c r="I105" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
-      <c r="A106" t="s">
+    <row r="106" spans="1:15">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
         <v>221</v>
       </c>
-      <c r="B106">
-        <v>1</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
         <v>213</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>222</v>
       </c>
-      <c r="E106" t="s">
-        <v>4</v>
-      </c>
-      <c r="N106" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
-      <c r="A107" t="s">
+      <c r="F106" t="s">
+        <v>4</v>
+      </c>
+      <c r="O106" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
         <v>478</v>
       </c>
-      <c r="B107">
-        <v>1</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107" t="s">
         <v>213</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>223</v>
       </c>
-      <c r="E107" t="s">
-        <v>4</v>
-      </c>
-      <c r="N107" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14">
-      <c r="A108" t="s">
+      <c r="F107" t="s">
+        <v>4</v>
+      </c>
+      <c r="O107" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
         <v>224</v>
       </c>
-      <c r="B108">
+      <c r="C108">
         <v>0</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>211</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
-      <c r="A109" t="s">
+    <row r="109" spans="1:15">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
         <v>479</v>
       </c>
-      <c r="B109">
+      <c r="C109">
         <v>0</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>213</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
-      <c r="A110" t="s">
+    <row r="110" spans="1:15">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
         <v>227</v>
       </c>
-      <c r="B110">
-        <v>1</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="s">
         <v>213</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>228</v>
       </c>
-      <c r="E110" t="s">
-        <v>4</v>
-      </c>
-      <c r="N110" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
-      <c r="A111" t="s">
+      <c r="F110" t="s">
+        <v>4</v>
+      </c>
+      <c r="O110" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
         <v>229</v>
       </c>
-      <c r="B111">
-        <v>1</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111" t="s">
         <v>211</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>230</v>
       </c>
-      <c r="E111" t="s">
-        <v>4</v>
-      </c>
-      <c r="H111" t="s">
-        <v>10</v>
+      <c r="F111" t="s">
+        <v>4</v>
       </c>
       <c r="I111" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J111" t="s">
         <v>31</v>
@@ -4545,306 +4879,357 @@
       <c r="K111" t="s">
         <v>31</v>
       </c>
-      <c r="M111" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14">
-      <c r="A112" t="s">
+      <c r="L111" t="s">
+        <v>31</v>
+      </c>
+      <c r="N111" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
         <v>480</v>
       </c>
-      <c r="B112">
-        <v>1</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="s">
         <v>213</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>231</v>
       </c>
-      <c r="E112" t="s">
-        <v>4</v>
-      </c>
-      <c r="N112" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" t="s">
+      <c r="F112" t="s">
+        <v>4</v>
+      </c>
+      <c r="O112" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
         <v>232</v>
       </c>
-      <c r="B113">
+      <c r="C113">
         <v>0</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>211</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
-      <c r="A114" t="s">
+    <row r="114" spans="1:15">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
         <v>234</v>
       </c>
-      <c r="B114">
+      <c r="C114">
         <v>0</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>213</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
-      <c r="A115" t="s">
+    <row r="115" spans="1:15">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
         <v>236</v>
       </c>
-      <c r="B115">
+      <c r="C115">
         <v>0</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>211</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
-      <c r="A116" t="s">
+    <row r="116" spans="1:15">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
         <v>238</v>
       </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
         <v>211</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>239</v>
       </c>
-      <c r="E116" t="s">
-        <v>4</v>
-      </c>
-      <c r="N116" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
-      <c r="A117" t="s">
+      <c r="F116" t="s">
+        <v>4</v>
+      </c>
+      <c r="O116" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
         <v>481</v>
       </c>
-      <c r="B117">
-        <v>1</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117" t="s">
         <v>213</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>240</v>
       </c>
-      <c r="E117" t="s">
-        <v>4</v>
-      </c>
-      <c r="N117" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
-      <c r="A118" t="s">
+      <c r="F117" t="s">
+        <v>4</v>
+      </c>
+      <c r="O117" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
         <v>241</v>
       </c>
-      <c r="B118">
-        <v>1</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
         <v>213</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>242</v>
       </c>
-      <c r="E118" t="s">
-        <v>4</v>
-      </c>
-      <c r="N118" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
-      <c r="A119" t="s">
+      <c r="F118" t="s">
+        <v>4</v>
+      </c>
+      <c r="O118" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
         <v>243</v>
       </c>
-      <c r="B119">
+      <c r="C119">
         <v>0</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>211</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
-      <c r="A120" t="s">
+    <row r="120" spans="1:15">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
         <v>245</v>
       </c>
-      <c r="B120">
+      <c r="C120">
         <v>0</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>211</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
-      <c r="A121" t="s">
+    <row r="121" spans="1:15">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
         <v>482</v>
       </c>
-      <c r="B121">
+      <c r="C121">
         <v>0</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>213</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
-      <c r="A122" t="s">
+    <row r="122" spans="1:15">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
         <v>248</v>
       </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="s">
         <v>211</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>249</v>
       </c>
-      <c r="E122" t="s">
-        <v>4</v>
-      </c>
-      <c r="F122">
+      <c r="F122" t="s">
+        <v>4</v>
+      </c>
+      <c r="G122">
         <v>140</v>
       </c>
-      <c r="H122" t="s">
+      <c r="I122" t="s">
         <v>36</v>
       </c>
-      <c r="J122" t="s">
-        <v>31</v>
-      </c>
       <c r="K122" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="123" spans="1:14">
-      <c r="A123" t="s">
+      <c r="L122" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
         <v>250</v>
       </c>
-      <c r="B123">
+      <c r="C123">
         <v>0</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>211</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
-      <c r="A124" t="s">
+    <row r="124" spans="1:15">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
         <v>252</v>
       </c>
-      <c r="B124">
+      <c r="C124">
         <v>0</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>211</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
-      <c r="A125" t="s">
+    <row r="125" spans="1:15">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
         <v>254</v>
       </c>
-      <c r="B125">
+      <c r="C125">
         <v>0</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>211</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
-      <c r="A126" t="s">
+    <row r="126" spans="1:15">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
         <v>256</v>
       </c>
-      <c r="B126">
+      <c r="C126">
         <v>0</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>211</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
-      <c r="A127" t="s">
+    <row r="127" spans="1:15">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
         <v>258</v>
       </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127" t="s">
         <v>211</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>259</v>
       </c>
-      <c r="E127" t="s">
-        <v>4</v>
-      </c>
-      <c r="N127" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14">
-      <c r="A128" t="s">
+      <c r="F127" t="s">
+        <v>4</v>
+      </c>
+      <c r="O127" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
         <v>260</v>
       </c>
-      <c r="B128">
-        <v>1</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128" t="s">
         <v>211</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>261</v>
       </c>
-      <c r="E128" t="s">
-        <v>4</v>
-      </c>
-      <c r="F128">
+      <c r="F128" t="s">
+        <v>4</v>
+      </c>
+      <c r="G128">
         <v>80</v>
       </c>
-      <c r="G128">
+      <c r="H128">
         <v>30</v>
       </c>
-      <c r="H128" t="s">
-        <v>10</v>
-      </c>
       <c r="I128" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J128" t="s">
         <v>31</v>
@@ -4852,147 +5237,171 @@
       <c r="K128" t="s">
         <v>31</v>
       </c>
-      <c r="M128" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14">
-      <c r="A129" t="s">
+      <c r="L128" t="s">
+        <v>31</v>
+      </c>
+      <c r="N128" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
         <v>262</v>
       </c>
-      <c r="B129">
-        <v>1</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129" t="s">
         <v>211</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>263</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
-      <c r="A130" t="s">
+    <row r="130" spans="1:15">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
         <v>264</v>
       </c>
-      <c r="B130">
+      <c r="C130">
         <v>0</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
         <v>211</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
-      <c r="A131" t="s">
+    <row r="131" spans="1:15">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
         <v>266</v>
       </c>
-      <c r="B131">
-        <v>1</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131" t="s">
         <v>267</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>268</v>
       </c>
-      <c r="E131" t="s">
-        <v>4</v>
-      </c>
-      <c r="F131">
+      <c r="F131" t="s">
+        <v>4</v>
+      </c>
+      <c r="G131">
         <v>110</v>
       </c>
-      <c r="H131" t="s">
+      <c r="I131" t="s">
         <v>269</v>
-      </c>
-      <c r="I131" t="s">
-        <v>6</v>
       </c>
       <c r="J131" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="132" spans="1:14">
-      <c r="A132" t="s">
+      <c r="K131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
         <v>270</v>
       </c>
-      <c r="B132">
+      <c r="C132">
         <v>0</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>267</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
-      <c r="A133" t="s">
+    <row r="133" spans="1:15">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
         <v>272</v>
       </c>
-      <c r="B133">
+      <c r="C133">
         <v>0</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>267</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
-      <c r="A134" t="s">
+    <row r="134" spans="1:15">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
         <v>274</v>
       </c>
-      <c r="B134">
+      <c r="C134">
         <v>0</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>267</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
-      <c r="A135" t="s">
+    <row r="135" spans="1:15">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
         <v>276</v>
       </c>
-      <c r="B135">
+      <c r="C135">
         <v>0</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
         <v>267</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
-      <c r="A136" t="s">
+    <row r="136" spans="1:15">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
         <v>278</v>
       </c>
-      <c r="B136">
-        <v>1</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136" t="s">
         <v>279</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
         <v>280</v>
       </c>
-      <c r="E136" t="s">
-        <v>10</v>
-      </c>
-      <c r="H136" t="s">
+      <c r="F136" t="s">
         <v>10</v>
       </c>
       <c r="I136" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J136" t="s">
         <v>6</v>
@@ -5000,481 +5409,547 @@
       <c r="K136" t="s">
         <v>6</v>
       </c>
-      <c r="M136" t="s">
-        <v>31</v>
+      <c r="L136" t="s">
+        <v>6</v>
       </c>
       <c r="N136" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14">
-      <c r="A137" t="s">
+        <v>31</v>
+      </c>
+      <c r="O136" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
         <v>281</v>
       </c>
-      <c r="B137">
-        <v>1</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="s">
         <v>267</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>282</v>
       </c>
-      <c r="E137" t="s">
-        <v>4</v>
-      </c>
-      <c r="F137">
+      <c r="F137" t="s">
+        <v>4</v>
+      </c>
+      <c r="G137">
         <v>13</v>
       </c>
-      <c r="H137" t="s">
+      <c r="I137" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
-      <c r="A138" t="s">
+    <row r="138" spans="1:15">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
         <v>283</v>
       </c>
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138" t="s">
         <v>267</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>284</v>
       </c>
-      <c r="E138" t="s">
-        <v>10</v>
-      </c>
-      <c r="H138" t="s">
-        <v>10</v>
-      </c>
-      <c r="N138" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14">
-      <c r="A139" t="s">
+      <c r="F138" t="s">
+        <v>10</v>
+      </c>
+      <c r="I138" t="s">
+        <v>10</v>
+      </c>
+      <c r="O138" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
         <v>285</v>
       </c>
-      <c r="B139">
-        <v>1</v>
-      </c>
-      <c r="C139" t="s">
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139" t="s">
         <v>267</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>286</v>
       </c>
-      <c r="E139" t="s">
-        <v>10</v>
-      </c>
-      <c r="F139">
+      <c r="F139" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139">
         <v>28</v>
       </c>
-      <c r="G139">
+      <c r="H139">
         <v>29</v>
       </c>
-      <c r="H139" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14">
-      <c r="A140" t="s">
+      <c r="I139" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
         <v>287</v>
       </c>
-      <c r="B140">
-        <v>1</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" t="s">
         <v>267</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>288</v>
       </c>
-      <c r="E140" t="s">
-        <v>10</v>
-      </c>
-      <c r="F140">
+      <c r="F140" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140">
         <v>267</v>
       </c>
-      <c r="H140" t="s">
+      <c r="I140" t="s">
         <v>36</v>
       </c>
-      <c r="I140" t="s">
-        <v>31</v>
-      </c>
       <c r="J140" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="K140" t="s">
         <v>6</v>
       </c>
-      <c r="M140" t="s">
+      <c r="L140" t="s">
         <v>6</v>
       </c>
       <c r="N140" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
-      <c r="A141" t="s">
+        <v>6</v>
+      </c>
+      <c r="O140" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
         <v>289</v>
       </c>
-      <c r="B141">
+      <c r="C141">
         <v>0</v>
       </c>
-      <c r="C141" t="s">
+      <c r="D141" t="s">
         <v>267</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
-      <c r="A142" t="s">
+    <row r="142" spans="1:15">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
         <v>291</v>
       </c>
-      <c r="B142">
+      <c r="C142">
         <v>0</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>267</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
-      <c r="A143" t="s">
+    <row r="143" spans="1:15">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
         <v>293</v>
       </c>
-      <c r="B143">
-        <v>1</v>
-      </c>
-      <c r="C143" t="s">
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="s">
         <v>267</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
         <v>294</v>
       </c>
-      <c r="E143" t="s">
-        <v>10</v>
-      </c>
-      <c r="F143">
+      <c r="F143" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143">
         <v>89</v>
       </c>
-      <c r="G143">
-        <v>10</v>
-      </c>
-      <c r="H143" t="s">
+      <c r="H143">
+        <v>10</v>
+      </c>
+      <c r="I143" t="s">
         <v>36</v>
       </c>
-      <c r="I143" t="s">
-        <v>31</v>
-      </c>
       <c r="J143" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="K143" t="s">
         <v>6</v>
       </c>
-      <c r="M143" t="s">
+      <c r="L143" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="144" spans="1:14">
-      <c r="A144" t="s">
+      <c r="N143" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
         <v>295</v>
       </c>
-      <c r="B144">
+      <c r="C144">
         <v>0</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>267</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
-      <c r="A145" t="s">
+    <row r="145" spans="1:15">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
         <v>297</v>
       </c>
-      <c r="B145">
+      <c r="C145">
         <v>0</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
         <v>267</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
-      <c r="A146" t="s">
+    <row r="146" spans="1:15">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
         <v>299</v>
       </c>
-      <c r="B146">
+      <c r="C146">
         <v>0</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
         <v>267</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
-      <c r="A147" t="s">
+    <row r="147" spans="1:15">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
         <v>301</v>
       </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
         <v>267</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
         <v>302</v>
       </c>
-      <c r="E147" t="s">
-        <v>4</v>
-      </c>
-      <c r="F147">
+      <c r="F147" t="s">
+        <v>4</v>
+      </c>
+      <c r="G147">
         <v>110</v>
       </c>
-      <c r="H147" t="s">
+      <c r="I147" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
-      <c r="A148" t="s">
+    <row r="148" spans="1:15">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
         <v>483</v>
       </c>
-      <c r="B148">
-        <v>1</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="C148">
+        <v>1</v>
+      </c>
+      <c r="D148" t="s">
         <v>279</v>
       </c>
-      <c r="D148" t="s">
+      <c r="E148" t="s">
         <v>303</v>
       </c>
-      <c r="E148" t="s">
-        <v>4</v>
-      </c>
-      <c r="H148" t="s">
+      <c r="F148" t="s">
+        <v>4</v>
+      </c>
+      <c r="I148" t="s">
         <v>36</v>
       </c>
-      <c r="N148" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14">
-      <c r="A149" t="s">
+      <c r="O148" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
         <v>304</v>
       </c>
-      <c r="B149">
-        <v>1</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149" t="s">
         <v>267</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
         <v>305</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
         <v>13</v>
       </c>
-      <c r="N149" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14">
-      <c r="A150" t="s">
+      <c r="O149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
         <v>306</v>
       </c>
-      <c r="B150">
+      <c r="C150">
         <v>0</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>267</v>
       </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
-      <c r="A151" t="s">
+    <row r="151" spans="1:15">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
         <v>308</v>
       </c>
-      <c r="B151">
+      <c r="C151">
         <v>0</v>
       </c>
-      <c r="C151" t="s">
+      <c r="D151" t="s">
         <v>267</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
-      <c r="A152" t="s">
+    <row r="152" spans="1:15">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
         <v>310</v>
       </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
         <v>267</v>
       </c>
-      <c r="D152" t="s">
+      <c r="E152" t="s">
         <v>311</v>
       </c>
-      <c r="E152" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152">
+      <c r="F152" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152">
         <v>40</v>
       </c>
-      <c r="H152" t="s">
+      <c r="I152" t="s">
         <v>36</v>
       </c>
-      <c r="N152" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14">
-      <c r="A153" t="s">
+      <c r="O152" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
         <v>312</v>
       </c>
-      <c r="B153">
-        <v>1</v>
-      </c>
-      <c r="C153" t="s">
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153" t="s">
         <v>267</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
         <v>313</v>
       </c>
-      <c r="E153" t="s">
-        <v>10</v>
-      </c>
-      <c r="H153" t="s">
-        <v>10</v>
-      </c>
-      <c r="N153" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14">
-      <c r="A154" t="s">
+      <c r="F153" t="s">
+        <v>10</v>
+      </c>
+      <c r="I153" t="s">
+        <v>10</v>
+      </c>
+      <c r="O153" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
         <v>314</v>
       </c>
-      <c r="B154">
+      <c r="C154">
         <v>0</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154" t="s">
         <v>279</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
-      <c r="A155" t="s">
+    <row r="155" spans="1:15">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
         <v>316</v>
       </c>
-      <c r="B155">
+      <c r="C155">
         <v>0</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
         <v>267</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
-      <c r="A156" t="s">
+    <row r="156" spans="1:15">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
         <v>318</v>
       </c>
-      <c r="B156">
-        <v>1</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156" t="s">
         <v>267</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" t="s">
         <v>319</v>
       </c>
-      <c r="E156" t="s">
-        <v>4</v>
-      </c>
-      <c r="F156">
+      <c r="F156" t="s">
+        <v>4</v>
+      </c>
+      <c r="G156">
         <v>82</v>
       </c>
-      <c r="G156">
+      <c r="H156">
         <v>50</v>
       </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
         <v>5</v>
       </c>
-      <c r="I156" t="s">
-        <v>31</v>
-      </c>
       <c r="J156" t="s">
+        <v>31</v>
+      </c>
+      <c r="K156" t="s">
         <v>6</v>
       </c>
-      <c r="K156" t="s">
-        <v>31</v>
-      </c>
       <c r="L156" t="s">
         <v>31</v>
       </c>
       <c r="M156" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="157" spans="1:14">
-      <c r="A157" t="s">
+      <c r="N156" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
         <v>320</v>
       </c>
-      <c r="B157">
+      <c r="C157">
         <v>0</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D157" t="s">
         <v>267</v>
       </c>
-      <c r="D157" t="s">
+      <c r="E157" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
-      <c r="A158" t="s">
+    <row r="158" spans="1:15">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
         <v>322</v>
       </c>
-      <c r="B158">
-        <v>1</v>
-      </c>
-      <c r="C158" t="s">
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158" t="s">
         <v>267</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
         <v>323</v>
       </c>
-      <c r="E158" t="s">
-        <v>4</v>
-      </c>
-      <c r="F158">
+      <c r="F158" t="s">
+        <v>4</v>
+      </c>
+      <c r="G158">
         <v>18</v>
       </c>
-      <c r="H158" t="s">
+      <c r="I158" t="s">
         <v>36</v>
-      </c>
-      <c r="I158" t="s">
-        <v>6</v>
       </c>
       <c r="J158" t="s">
         <v>6</v>
@@ -5482,705 +5957,792 @@
       <c r="K158" t="s">
         <v>6</v>
       </c>
-      <c r="M158" t="s">
+      <c r="L158" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="159" spans="1:14">
-      <c r="A159" t="s">
+      <c r="N158" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
         <v>324</v>
       </c>
-      <c r="B159">
-        <v>1</v>
-      </c>
-      <c r="C159" t="s">
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159" t="s">
         <v>267</v>
       </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
         <v>325</v>
       </c>
-      <c r="E159" t="s">
-        <v>4</v>
-      </c>
-      <c r="H159" t="s">
-        <v>10</v>
-      </c>
-      <c r="N159" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14">
-      <c r="A160" t="s">
+      <c r="F159" t="s">
+        <v>4</v>
+      </c>
+      <c r="I159" t="s">
+        <v>10</v>
+      </c>
+      <c r="O159" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
         <v>326</v>
       </c>
-      <c r="B160">
-        <v>1</v>
-      </c>
-      <c r="C160" t="s">
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160" t="s">
         <v>267</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>327</v>
       </c>
-      <c r="E160" t="s">
-        <v>4</v>
-      </c>
-      <c r="F160">
+      <c r="F160" t="s">
+        <v>4</v>
+      </c>
+      <c r="G160">
         <v>55</v>
       </c>
-      <c r="G160">
+      <c r="H160">
         <v>8</v>
       </c>
-      <c r="H160" t="s">
+      <c r="I160" t="s">
         <v>5</v>
       </c>
-      <c r="I160" t="s">
-        <v>31</v>
-      </c>
       <c r="J160" t="s">
         <v>31</v>
       </c>
-      <c r="N160" t="s">
+      <c r="K160" t="s">
+        <v>31</v>
+      </c>
+      <c r="O160" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
-      <c r="A161" t="s">
+    <row r="161" spans="1:15">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
         <v>328</v>
       </c>
-      <c r="B161">
+      <c r="C161">
         <v>0</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" t="s">
         <v>267</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="162" spans="1:14">
-      <c r="A162" t="s">
+    <row r="162" spans="1:15">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
         <v>330</v>
       </c>
-      <c r="B162">
+      <c r="C162">
         <v>0</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
         <v>267</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
-      <c r="A163" t="s">
+    <row r="163" spans="1:15">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
         <v>332</v>
       </c>
-      <c r="B163">
-        <v>1</v>
-      </c>
-      <c r="C163" t="s">
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
         <v>333</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>334</v>
       </c>
-      <c r="E163" t="s">
-        <v>10</v>
-      </c>
-      <c r="H163" t="s">
+      <c r="F163" t="s">
+        <v>10</v>
+      </c>
+      <c r="I163" t="s">
         <v>5</v>
-      </c>
-      <c r="I163" t="s">
-        <v>6</v>
       </c>
       <c r="J163" t="s">
         <v>6</v>
       </c>
-      <c r="L163" t="s">
+      <c r="K163" t="s">
         <v>6</v>
       </c>
-      <c r="N163" t="s">
+      <c r="M163" t="s">
+        <v>6</v>
+      </c>
+      <c r="O163" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
-      <c r="A164" t="s">
+    <row r="164" spans="1:15">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
         <v>335</v>
       </c>
-      <c r="B164">
-        <v>1</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164" t="s">
         <v>336</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>337</v>
       </c>
-      <c r="E164" t="s">
-        <v>4</v>
-      </c>
-      <c r="F164">
+      <c r="F164" t="s">
+        <v>4</v>
+      </c>
+      <c r="G164">
         <v>37</v>
       </c>
-      <c r="H164" t="s">
-        <v>10</v>
-      </c>
-      <c r="N164" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14">
-      <c r="A165" t="s">
+      <c r="I164" t="s">
+        <v>10</v>
+      </c>
+      <c r="O164" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
         <v>338</v>
       </c>
-      <c r="B165">
-        <v>1</v>
-      </c>
-      <c r="C165" t="s">
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165" t="s">
         <v>333</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>339</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>13</v>
       </c>
-      <c r="I165" t="s">
-        <v>31</v>
-      </c>
       <c r="J165" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="166" spans="1:14">
-      <c r="A166" t="s">
+      <c r="K165" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
         <v>340</v>
       </c>
-      <c r="B166">
-        <v>1</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166" t="s">
         <v>333</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
         <v>341</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>13</v>
       </c>
-      <c r="J166" t="s">
+      <c r="K166" t="s">
         <v>6</v>
       </c>
-      <c r="N166" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14">
-      <c r="A167" t="s">
+      <c r="O166" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
         <v>342</v>
       </c>
-      <c r="B167">
-        <v>1</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" t="s">
         <v>333</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>343</v>
       </c>
-      <c r="E167" t="s">
-        <v>4</v>
-      </c>
-      <c r="F167">
+      <c r="F167" t="s">
+        <v>4</v>
+      </c>
+      <c r="G167">
         <v>15</v>
       </c>
-      <c r="H167" t="s">
+      <c r="I167" t="s">
         <v>5</v>
       </c>
-      <c r="I167" t="s">
-        <v>31</v>
-      </c>
       <c r="J167" t="s">
         <v>31</v>
       </c>
-      <c r="L167" t="s">
-        <v>31</v>
-      </c>
-      <c r="N167" t="s">
+      <c r="K167" t="s">
+        <v>31</v>
+      </c>
+      <c r="M167" t="s">
+        <v>31</v>
+      </c>
+      <c r="O167" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
-      <c r="A168" t="s">
+    <row r="168" spans="1:15">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
         <v>344</v>
       </c>
-      <c r="B168">
+      <c r="C168">
         <v>0</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>333</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
-      <c r="A169" t="s">
+    <row r="169" spans="1:15">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
         <v>346</v>
       </c>
-      <c r="B169">
-        <v>1</v>
-      </c>
-      <c r="C169" t="s">
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169" t="s">
         <v>333</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
         <v>347</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
         <v>13</v>
       </c>
-      <c r="I169" t="s">
-        <v>31</v>
-      </c>
-      <c r="K169" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14">
-      <c r="A170" t="s">
+      <c r="J169" t="s">
+        <v>31</v>
+      </c>
+      <c r="L169" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
         <v>348</v>
       </c>
-      <c r="B170">
+      <c r="C170">
         <v>0</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>333</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
-      <c r="A171" t="s">
+    <row r="171" spans="1:15">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
         <v>350</v>
       </c>
-      <c r="B171">
-        <v>1</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" t="s">
         <v>333</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>351</v>
       </c>
-      <c r="E171" t="s">
-        <v>4</v>
-      </c>
-      <c r="F171">
-        <v>10</v>
-      </c>
-      <c r="H171" t="s">
+      <c r="F171" t="s">
+        <v>4</v>
+      </c>
+      <c r="G171">
+        <v>10</v>
+      </c>
+      <c r="I171" t="s">
         <v>5</v>
       </c>
-      <c r="I171" t="s">
-        <v>31</v>
-      </c>
       <c r="J171" t="s">
         <v>31</v>
       </c>
       <c r="K171" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="172" spans="1:14">
-      <c r="A172" t="s">
+      <c r="L171" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
         <v>352</v>
       </c>
-      <c r="B172">
-        <v>1</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172" t="s">
         <v>333</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>353</v>
       </c>
-      <c r="E172" t="s">
-        <v>4</v>
-      </c>
-      <c r="F172">
+      <c r="F172" t="s">
+        <v>4</v>
+      </c>
+      <c r="G172">
         <v>68</v>
       </c>
-      <c r="H172" t="s">
-        <v>10</v>
-      </c>
-      <c r="N172" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14">
-      <c r="A173" t="s">
+      <c r="I172" t="s">
+        <v>10</v>
+      </c>
+      <c r="O172" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
         <v>354</v>
       </c>
-      <c r="B173">
-        <v>1</v>
-      </c>
-      <c r="C173" t="s">
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" t="s">
         <v>333</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>355</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
-      <c r="A174" t="s">
+    <row r="174" spans="1:15">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
         <v>356</v>
       </c>
-      <c r="B174">
-        <v>1</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="D174" t="s">
         <v>333</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>357</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>13</v>
       </c>
-      <c r="I174" t="s">
-        <v>31</v>
-      </c>
       <c r="J174" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="175" spans="1:14">
-      <c r="A175" t="s">
+      <c r="K174" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
         <v>358</v>
       </c>
-      <c r="B175">
-        <v>1</v>
-      </c>
-      <c r="C175" t="s">
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175" t="s">
         <v>333</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>359</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>13</v>
       </c>
-      <c r="I175" t="s">
-        <v>31</v>
-      </c>
       <c r="J175" t="s">
         <v>31</v>
       </c>
-      <c r="N175" t="s">
+      <c r="K175" t="s">
+        <v>31</v>
+      </c>
+      <c r="O175" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
-      <c r="A176" t="s">
+    <row r="176" spans="1:15">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
         <v>360</v>
       </c>
-      <c r="B176">
-        <v>1</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176" t="s">
         <v>336</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
         <v>361</v>
       </c>
-      <c r="E176" t="s">
-        <v>4</v>
-      </c>
-      <c r="F176">
+      <c r="F176" t="s">
+        <v>4</v>
+      </c>
+      <c r="G176">
         <v>20</v>
       </c>
-      <c r="H176" t="s">
-        <v>10</v>
-      </c>
-      <c r="N176" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14">
-      <c r="A177" t="s">
+      <c r="I176" t="s">
+        <v>10</v>
+      </c>
+      <c r="O176" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
         <v>362</v>
       </c>
-      <c r="B177">
+      <c r="C177">
         <v>0</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>333</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
-      <c r="A178" t="s">
+    <row r="178" spans="1:15">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
         <v>364</v>
       </c>
-      <c r="B178">
-        <v>1</v>
-      </c>
-      <c r="C178" t="s">
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178" t="s">
         <v>333</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>365</v>
       </c>
-      <c r="E178" t="s">
-        <v>10</v>
-      </c>
-      <c r="H178" t="s">
+      <c r="F178" t="s">
+        <v>10</v>
+      </c>
+      <c r="I178" t="s">
         <v>5</v>
       </c>
-      <c r="N178" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14">
-      <c r="A179" t="s">
+      <c r="O178" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
         <v>366</v>
       </c>
-      <c r="B179">
-        <v>1</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179" t="s">
         <v>333</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
         <v>484</v>
       </c>
-      <c r="E179" t="s">
-        <v>10</v>
-      </c>
-      <c r="H179" t="s">
+      <c r="F179" t="s">
+        <v>10</v>
+      </c>
+      <c r="I179" t="s">
         <v>5</v>
       </c>
-      <c r="I179" t="s">
-        <v>31</v>
-      </c>
       <c r="J179" t="s">
         <v>31</v>
       </c>
-      <c r="L179" t="s">
-        <v>31</v>
-      </c>
-      <c r="N179" t="s">
+      <c r="K179" t="s">
+        <v>31</v>
+      </c>
+      <c r="M179" t="s">
+        <v>31</v>
+      </c>
+      <c r="O179" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
-      <c r="A180" t="s">
+    <row r="180" spans="1:15">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
         <v>367</v>
       </c>
-      <c r="B180">
-        <v>1</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180" t="s">
         <v>333</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>368</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>13</v>
       </c>
-      <c r="I180" t="s">
-        <v>31</v>
-      </c>
-      <c r="L180" t="s">
-        <v>31</v>
-      </c>
-      <c r="N180" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14">
-      <c r="A181" t="s">
+      <c r="J180" t="s">
+        <v>31</v>
+      </c>
+      <c r="M180" t="s">
+        <v>31</v>
+      </c>
+      <c r="O180" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
         <v>369</v>
       </c>
-      <c r="B181">
-        <v>1</v>
-      </c>
-      <c r="C181" t="s">
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181" t="s">
         <v>333</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>370</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>13</v>
       </c>
-      <c r="I181" t="s">
-        <v>31</v>
-      </c>
-      <c r="N181" t="s">
+      <c r="J181" t="s">
+        <v>31</v>
+      </c>
+      <c r="O181" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
-      <c r="A182" t="s">
+    <row r="182" spans="1:15">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
         <v>371</v>
       </c>
-      <c r="B182">
-        <v>1</v>
-      </c>
-      <c r="C182" t="s">
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182" t="s">
         <v>333</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>372</v>
       </c>
-      <c r="E182" t="s">
-        <v>10</v>
-      </c>
-      <c r="F182">
+      <c r="F182" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182">
         <v>22</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>36</v>
       </c>
-      <c r="I182" t="s">
-        <v>31</v>
-      </c>
       <c r="J182" t="s">
         <v>31</v>
       </c>
-      <c r="N182" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14">
-      <c r="A183" t="s">
+      <c r="K182" t="s">
+        <v>31</v>
+      </c>
+      <c r="O182" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
         <v>373</v>
       </c>
-      <c r="B183">
-        <v>1</v>
-      </c>
-      <c r="C183" t="s">
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183" t="s">
         <v>333</v>
       </c>
-      <c r="D183" t="s">
+      <c r="E183" t="s">
         <v>374</v>
       </c>
-      <c r="E183" t="s">
-        <v>10</v>
-      </c>
-      <c r="F183">
+      <c r="F183" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183">
         <v>35</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>36</v>
       </c>
-      <c r="I183" t="s">
-        <v>31</v>
-      </c>
       <c r="J183" t="s">
         <v>31</v>
       </c>
-      <c r="L183" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14">
-      <c r="A184" t="s">
+      <c r="K183" t="s">
+        <v>31</v>
+      </c>
+      <c r="M183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
         <v>375</v>
       </c>
-      <c r="B184">
+      <c r="C184">
         <v>0</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
         <v>333</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
-      <c r="A185" t="s">
+    <row r="185" spans="1:15">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
         <v>377</v>
       </c>
-      <c r="B185">
-        <v>1</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185" t="s">
         <v>336</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>378</v>
       </c>
-      <c r="E185" t="s">
-        <v>4</v>
-      </c>
-      <c r="F185">
+      <c r="F185" t="s">
+        <v>4</v>
+      </c>
+      <c r="G185">
         <v>15</v>
       </c>
-      <c r="H185" t="s">
-        <v>10</v>
-      </c>
-      <c r="N185" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14">
-      <c r="A186" t="s">
+      <c r="I185" t="s">
+        <v>10</v>
+      </c>
+      <c r="O185" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
         <v>379</v>
       </c>
-      <c r="B186">
-        <v>1</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="s">
         <v>333</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>380</v>
       </c>
-      <c r="E186" t="s">
-        <v>10</v>
-      </c>
-      <c r="H186" t="s">
+      <c r="F186" t="s">
         <v>10</v>
       </c>
       <c r="I186" t="s">
-        <v>31</v>
-      </c>
-      <c r="L186" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="187" spans="1:14">
-      <c r="A187" t="s">
+        <v>10</v>
+      </c>
+      <c r="J186" t="s">
+        <v>31</v>
+      </c>
+      <c r="M186" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
         <v>381</v>
       </c>
-      <c r="B187">
-        <v>1</v>
-      </c>
-      <c r="C187" t="s">
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="s">
         <v>333</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>382</v>
       </c>
-      <c r="E187" t="s">
-        <v>10</v>
-      </c>
-      <c r="H187" t="s">
+      <c r="F187" t="s">
         <v>10</v>
       </c>
       <c r="I187" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J187" t="s">
         <v>31</v>
@@ -6191,139 +6753,154 @@
       <c r="L187" t="s">
         <v>31</v>
       </c>
-      <c r="N187" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14">
-      <c r="A188" t="s">
+      <c r="M187" t="s">
+        <v>31</v>
+      </c>
+      <c r="O187" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
         <v>383</v>
       </c>
-      <c r="B188">
-        <v>1</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
         <v>336</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>384</v>
       </c>
-      <c r="E188" t="s">
-        <v>4</v>
-      </c>
-      <c r="F188">
+      <c r="F188" t="s">
+        <v>4</v>
+      </c>
+      <c r="G188">
         <v>13</v>
       </c>
-      <c r="H188" t="s">
-        <v>10</v>
-      </c>
-      <c r="N188" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14">
-      <c r="A189" t="s">
+      <c r="I188" t="s">
+        <v>10</v>
+      </c>
+      <c r="O188" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
         <v>385</v>
       </c>
-      <c r="B189">
-        <v>1</v>
-      </c>
-      <c r="C189" t="s">
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189" t="s">
         <v>336</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>386</v>
       </c>
-      <c r="E189" t="s">
-        <v>4</v>
-      </c>
-      <c r="F189">
+      <c r="F189" t="s">
+        <v>4</v>
+      </c>
+      <c r="G189">
         <v>12</v>
       </c>
-      <c r="H189" t="s">
-        <v>10</v>
-      </c>
-      <c r="N189" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14">
-      <c r="A190" t="s">
+      <c r="I189" t="s">
+        <v>10</v>
+      </c>
+      <c r="O189" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
         <v>387</v>
       </c>
-      <c r="B190">
-        <v>1</v>
-      </c>
-      <c r="C190" t="s">
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190" t="s">
         <v>333</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>388</v>
       </c>
-      <c r="E190" t="s">
-        <v>10</v>
-      </c>
-      <c r="H190" t="s">
+      <c r="F190" t="s">
         <v>10</v>
       </c>
       <c r="I190" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J190" t="s">
         <v>31</v>
       </c>
-      <c r="L190" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14">
-      <c r="A191" t="s">
+      <c r="K190" t="s">
+        <v>31</v>
+      </c>
+      <c r="M190" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
         <v>389</v>
       </c>
-      <c r="B191">
-        <v>1</v>
-      </c>
-      <c r="C191" t="s">
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191" t="s">
         <v>333</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
         <v>390</v>
       </c>
-      <c r="E191" t="s">
-        <v>10</v>
-      </c>
-      <c r="H191" t="s">
+      <c r="F191" t="s">
         <v>10</v>
       </c>
       <c r="I191" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J191" t="s">
         <v>31</v>
       </c>
-      <c r="N191" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14">
-      <c r="A192" t="s">
+      <c r="K191" t="s">
+        <v>31</v>
+      </c>
+      <c r="O191" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
         <v>391</v>
       </c>
-      <c r="B192">
-        <v>1</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="s">
         <v>333</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
         <v>392</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>13</v>
       </c>
-      <c r="I192" t="s">
-        <v>31</v>
-      </c>
       <c r="J192" t="s">
         <v>31</v>
       </c>
@@ -6336,419 +6913,473 @@
       <c r="M192" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="193" spans="1:14">
-      <c r="A193" t="s">
+      <c r="N192" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
         <v>393</v>
       </c>
-      <c r="B193">
-        <v>1</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193" t="s">
         <v>333</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" t="s">
         <v>394</v>
       </c>
-      <c r="E193" t="s">
-        <v>4</v>
-      </c>
-      <c r="H193" t="s">
-        <v>10</v>
-      </c>
-      <c r="N193" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14">
-      <c r="A194" t="s">
+      <c r="F193" t="s">
+        <v>4</v>
+      </c>
+      <c r="I193" t="s">
+        <v>10</v>
+      </c>
+      <c r="O193" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
         <v>395</v>
       </c>
-      <c r="B194">
-        <v>1</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
         <v>333</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>396</v>
       </c>
-      <c r="E194" t="s">
-        <v>4</v>
-      </c>
-      <c r="H194" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14">
-      <c r="A195" t="s">
+      <c r="F194" t="s">
+        <v>4</v>
+      </c>
+      <c r="I194" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
         <v>397</v>
       </c>
-      <c r="B195">
+      <c r="C195">
         <v>0</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
         <v>333</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="196" spans="1:14">
-      <c r="A196" t="s">
+    <row r="196" spans="1:15">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
         <v>399</v>
       </c>
-      <c r="B196">
+      <c r="C196">
         <v>0</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
         <v>400</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="197" spans="1:14">
-      <c r="A197" t="s">
+    <row r="197" spans="1:15">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
         <v>402</v>
       </c>
-      <c r="B197">
-        <v>1</v>
-      </c>
-      <c r="C197" t="s">
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="s">
         <v>400</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>403</v>
       </c>
-      <c r="E197" t="s">
-        <v>4</v>
-      </c>
-      <c r="F197">
+      <c r="F197" t="s">
+        <v>4</v>
+      </c>
+      <c r="G197">
         <v>25</v>
       </c>
-      <c r="G197">
-        <v>10</v>
-      </c>
-      <c r="H197" t="s">
+      <c r="H197">
+        <v>10</v>
+      </c>
+      <c r="I197" t="s">
         <v>5</v>
-      </c>
-      <c r="I197" t="s">
-        <v>6</v>
       </c>
       <c r="J197" t="s">
         <v>6</v>
       </c>
-      <c r="L197" t="s">
+      <c r="K197" t="s">
         <v>6</v>
       </c>
-      <c r="N197" t="s">
+      <c r="M197" t="s">
+        <v>6</v>
+      </c>
+      <c r="O197" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:14">
-      <c r="A198" t="s">
+    <row r="198" spans="1:15">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
         <v>404</v>
       </c>
-      <c r="B198">
-        <v>1</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198" t="s">
         <v>405</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>406</v>
       </c>
-      <c r="E198" t="s">
-        <v>4</v>
-      </c>
-      <c r="F198">
+      <c r="F198" t="s">
+        <v>4</v>
+      </c>
+      <c r="G198">
         <v>39</v>
       </c>
-      <c r="H198" t="s">
-        <v>10</v>
-      </c>
-      <c r="N198" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="199" spans="1:14">
-      <c r="A199" t="s">
+      <c r="I198" t="s">
+        <v>10</v>
+      </c>
+      <c r="O198" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
         <v>407</v>
       </c>
-      <c r="B199">
-        <v>1</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199" t="s">
         <v>405</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
         <v>408</v>
       </c>
-      <c r="E199" t="s">
-        <v>4</v>
-      </c>
-      <c r="F199">
+      <c r="F199" t="s">
+        <v>4</v>
+      </c>
+      <c r="G199">
         <v>30</v>
       </c>
-      <c r="H199" t="s">
-        <v>10</v>
-      </c>
-      <c r="N199" t="s">
+      <c r="I199" t="s">
+        <v>10</v>
+      </c>
+      <c r="O199" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:14">
-      <c r="A200" t="s">
+    <row r="200" spans="1:15">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
         <v>409</v>
       </c>
-      <c r="B200">
-        <v>1</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200" t="s">
         <v>405</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
         <v>410</v>
       </c>
-      <c r="E200" t="s">
-        <v>4</v>
-      </c>
-      <c r="F200">
+      <c r="F200" t="s">
+        <v>4</v>
+      </c>
+      <c r="G200">
         <v>15</v>
       </c>
-      <c r="H200" t="s">
-        <v>10</v>
-      </c>
-      <c r="N200" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14">
-      <c r="A201" t="s">
+      <c r="I200" t="s">
+        <v>10</v>
+      </c>
+      <c r="O200" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
         <v>411</v>
       </c>
-      <c r="B201">
-        <v>1</v>
-      </c>
-      <c r="C201" t="s">
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201" t="s">
         <v>405</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
         <v>412</v>
       </c>
-      <c r="E201" t="s">
-        <v>4</v>
-      </c>
-      <c r="F201">
-        <v>10</v>
-      </c>
-      <c r="H201" t="s">
+      <c r="F201" t="s">
+        <v>4</v>
+      </c>
+      <c r="G201">
+        <v>10</v>
+      </c>
+      <c r="I201" t="s">
         <v>5</v>
       </c>
-      <c r="N201" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14">
-      <c r="A202" t="s">
+      <c r="O201" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
         <v>413</v>
       </c>
-      <c r="B202">
-        <v>1</v>
-      </c>
-      <c r="C202" t="s">
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="D202" t="s">
         <v>400</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" t="s">
         <v>414</v>
       </c>
-      <c r="E202" t="s">
-        <v>4</v>
-      </c>
-      <c r="F202">
+      <c r="F202" t="s">
+        <v>4</v>
+      </c>
+      <c r="G202">
         <v>16</v>
       </c>
-      <c r="H202" t="s">
+      <c r="I202" t="s">
         <v>5</v>
       </c>
-      <c r="N202" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14">
-      <c r="A203" t="s">
+      <c r="O202" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
         <v>415</v>
       </c>
-      <c r="B203">
+      <c r="C203">
         <v>0</v>
       </c>
-      <c r="C203" t="s">
+      <c r="D203" t="s">
         <v>400</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="204" spans="1:14">
-      <c r="A204" t="s">
+    <row r="204" spans="1:15">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
         <v>417</v>
       </c>
-      <c r="B204">
-        <v>1</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
         <v>405</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
         <v>418</v>
       </c>
-      <c r="E204" t="s">
-        <v>4</v>
-      </c>
-      <c r="F204">
+      <c r="F204" t="s">
+        <v>4</v>
+      </c>
+      <c r="G204">
         <v>33</v>
       </c>
-      <c r="H204" t="s">
-        <v>10</v>
-      </c>
-      <c r="N204" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14">
-      <c r="A205" t="s">
+      <c r="I204" t="s">
+        <v>10</v>
+      </c>
+      <c r="O204" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
         <v>419</v>
       </c>
-      <c r="B205">
+      <c r="C205">
         <v>0</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205" t="s">
         <v>405</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="206" spans="1:14">
-      <c r="A206" t="s">
+    <row r="206" spans="1:15">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
         <v>421</v>
       </c>
-      <c r="B206">
+      <c r="C206">
         <v>0</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
         <v>400</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
-      <c r="A207" t="s">
+    <row r="207" spans="1:15">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
         <v>422</v>
       </c>
-      <c r="B207">
-        <v>1</v>
-      </c>
-      <c r="C207" t="s">
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207" t="s">
         <v>405</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>423</v>
       </c>
-      <c r="E207" t="s">
-        <v>4</v>
-      </c>
-      <c r="F207">
+      <c r="F207" t="s">
+        <v>4</v>
+      </c>
+      <c r="G207">
         <v>32</v>
       </c>
-      <c r="H207" t="s">
-        <v>10</v>
-      </c>
-      <c r="N207" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14">
-      <c r="A208" t="s">
+      <c r="I207" t="s">
+        <v>10</v>
+      </c>
+      <c r="O207" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
         <v>424</v>
       </c>
-      <c r="B208">
-        <v>1</v>
-      </c>
-      <c r="C208" t="s">
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208" t="s">
         <v>400</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
         <v>425</v>
       </c>
-      <c r="E208" t="s">
-        <v>4</v>
-      </c>
-      <c r="F208">
+      <c r="F208" t="s">
+        <v>4</v>
+      </c>
+      <c r="G208">
         <v>20</v>
       </c>
-      <c r="H208" t="s">
+      <c r="I208" t="s">
         <v>5</v>
       </c>
-      <c r="J208" t="s">
+      <c r="K208" t="s">
         <v>6</v>
       </c>
-      <c r="N208" t="s">
+      <c r="O208" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
-      <c r="A209" t="s">
+    <row r="209" spans="1:15">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
         <v>426</v>
       </c>
-      <c r="B209">
-        <v>1</v>
-      </c>
-      <c r="C209" t="s">
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209" t="s">
         <v>405</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
         <v>427</v>
       </c>
-      <c r="E209" t="s">
-        <v>4</v>
-      </c>
-      <c r="F209">
+      <c r="F209" t="s">
+        <v>4</v>
+      </c>
+      <c r="G209">
         <v>66</v>
       </c>
-      <c r="H209" t="s">
-        <v>10</v>
-      </c>
-      <c r="N209" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14">
-      <c r="A210" t="s">
+      <c r="I209" t="s">
+        <v>10</v>
+      </c>
+      <c r="O209" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
         <v>428</v>
       </c>
-      <c r="B210">
-        <v>1</v>
-      </c>
-      <c r="C210" t="s">
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210" t="s">
         <v>400</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>429</v>
       </c>
-      <c r="E210" t="s">
-        <v>4</v>
-      </c>
-      <c r="F210">
+      <c r="F210" t="s">
+        <v>4</v>
+      </c>
+      <c r="G210">
         <v>150</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>5</v>
-      </c>
-      <c r="I210" t="s">
-        <v>6</v>
       </c>
       <c r="J210" t="s">
         <v>6</v>
@@ -6756,330 +7387,372 @@
       <c r="K210" t="s">
         <v>6</v>
       </c>
-      <c r="M210" t="s">
+      <c r="L210" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="211" spans="1:14">
-      <c r="A211" t="s">
+      <c r="N210" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
         <v>430</v>
       </c>
-      <c r="B211">
+      <c r="C211">
         <v>0</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211" t="s">
         <v>400</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
-      <c r="A212" t="s">
+    <row r="212" spans="1:15">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
         <v>432</v>
       </c>
-      <c r="B212">
+      <c r="C212">
         <v>0</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
         <v>400</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
-      <c r="A213" t="s">
+    <row r="213" spans="1:15">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
         <v>434</v>
       </c>
-      <c r="B213">
+      <c r="C213">
         <v>0</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213" t="s">
         <v>405</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
-      <c r="A214" t="s">
+    <row r="214" spans="1:15">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
         <v>436</v>
       </c>
-      <c r="B214">
-        <v>1</v>
-      </c>
-      <c r="C214" t="s">
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="D214" t="s">
         <v>405</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>437</v>
       </c>
-      <c r="E214" t="s">
-        <v>4</v>
-      </c>
-      <c r="F214">
+      <c r="F214" t="s">
+        <v>4</v>
+      </c>
+      <c r="G214">
         <v>6</v>
       </c>
-      <c r="H214" t="s">
-        <v>10</v>
-      </c>
-      <c r="N214" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="215" spans="1:14">
-      <c r="A215" t="s">
+      <c r="I214" t="s">
+        <v>10</v>
+      </c>
+      <c r="O214" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
         <v>438</v>
       </c>
-      <c r="B215">
-        <v>1</v>
-      </c>
-      <c r="C215" t="s">
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215" t="s">
         <v>405</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>439</v>
       </c>
-      <c r="E215" t="s">
-        <v>4</v>
-      </c>
-      <c r="F215">
+      <c r="F215" t="s">
+        <v>4</v>
+      </c>
+      <c r="G215">
         <v>20</v>
       </c>
-      <c r="H215" t="s">
-        <v>10</v>
-      </c>
-      <c r="N215" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14">
-      <c r="A216" t="s">
+      <c r="I215" t="s">
+        <v>10</v>
+      </c>
+      <c r="O215" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
         <v>440</v>
       </c>
-      <c r="B216">
-        <v>1</v>
-      </c>
-      <c r="C216" t="s">
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216" t="s">
         <v>405</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>441</v>
       </c>
-      <c r="E216" t="s">
-        <v>4</v>
-      </c>
-      <c r="F216">
+      <c r="F216" t="s">
+        <v>4</v>
+      </c>
+      <c r="G216">
         <v>13</v>
       </c>
-      <c r="H216" t="s">
-        <v>10</v>
-      </c>
-      <c r="N216" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="217" spans="1:14">
-      <c r="A217" t="s">
+      <c r="I216" t="s">
+        <v>10</v>
+      </c>
+      <c r="O216" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
         <v>442</v>
       </c>
-      <c r="B217">
-        <v>1</v>
-      </c>
-      <c r="C217" t="s">
+      <c r="C217">
+        <v>1</v>
+      </c>
+      <c r="D217" t="s">
         <v>400</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>443</v>
       </c>
-      <c r="E217" t="s">
-        <v>4</v>
-      </c>
-      <c r="F217">
+      <c r="F217" t="s">
+        <v>4</v>
+      </c>
+      <c r="G217">
         <v>95</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>5</v>
       </c>
-      <c r="J217" t="s">
+      <c r="K217" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
-      <c r="A218" t="s">
+    <row r="218" spans="1:15">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
         <v>444</v>
       </c>
-      <c r="B218">
-        <v>1</v>
-      </c>
-      <c r="C218" t="s">
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218" t="s">
         <v>445</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>446</v>
       </c>
-      <c r="E218" t="s">
-        <v>4</v>
-      </c>
-      <c r="F218">
+      <c r="F218" t="s">
+        <v>4</v>
+      </c>
+      <c r="G218">
         <v>93</v>
       </c>
-      <c r="G218">
-        <v>10</v>
-      </c>
-      <c r="H218" t="s">
+      <c r="H218">
+        <v>10</v>
+      </c>
+      <c r="I218" t="s">
         <v>36</v>
       </c>
-      <c r="I218" t="s">
-        <v>31</v>
-      </c>
       <c r="J218" t="s">
         <v>31</v>
       </c>
       <c r="K218" t="s">
         <v>31</v>
       </c>
-      <c r="M218" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="219" spans="1:14">
-      <c r="A219" t="s">
+      <c r="L218" t="s">
+        <v>31</v>
+      </c>
+      <c r="N218" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
         <v>447</v>
       </c>
-      <c r="B219">
-        <v>1</v>
-      </c>
-      <c r="C219" t="s">
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219" t="s">
         <v>445</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>448</v>
       </c>
-      <c r="E219" t="s">
-        <v>4</v>
-      </c>
-      <c r="H219" t="s">
+      <c r="F219" t="s">
+        <v>4</v>
+      </c>
+      <c r="I219" t="s">
         <v>5</v>
       </c>
-      <c r="N219" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14">
-      <c r="A220" t="s">
+      <c r="O219" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
         <v>449</v>
       </c>
-      <c r="B220">
-        <v>1</v>
-      </c>
-      <c r="C220" t="s">
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220" t="s">
         <v>450</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
         <v>451</v>
       </c>
-      <c r="E220" t="s">
-        <v>4</v>
-      </c>
-      <c r="H220" t="s">
+      <c r="F220" t="s">
+        <v>4</v>
+      </c>
+      <c r="I220" t="s">
         <v>5</v>
       </c>
-      <c r="N220" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14">
-      <c r="A221" t="s">
+      <c r="O220" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
         <v>452</v>
       </c>
-      <c r="B221">
+      <c r="C221">
         <v>0</v>
       </c>
-      <c r="C221" t="s">
+      <c r="D221" t="s">
         <v>445</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="222" spans="1:14">
-      <c r="A222" t="s">
+    <row r="222" spans="1:15">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
         <v>454</v>
       </c>
-      <c r="B222">
-        <v>1</v>
-      </c>
-      <c r="C222" t="s">
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222" t="s">
         <v>445</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>455</v>
       </c>
-      <c r="E222" t="s">
-        <v>4</v>
-      </c>
-      <c r="F222">
+      <c r="F222" t="s">
+        <v>4</v>
+      </c>
+      <c r="G222">
         <v>40</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>36</v>
       </c>
-      <c r="N222" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14">
-      <c r="A223" t="s">
+      <c r="O222" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
         <v>456</v>
       </c>
-      <c r="B223">
-        <v>1</v>
-      </c>
-      <c r="C223" t="s">
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="s">
         <v>445</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>457</v>
       </c>
-      <c r="E223" t="s">
-        <v>4</v>
-      </c>
-      <c r="F223">
+      <c r="F223" t="s">
+        <v>4</v>
+      </c>
+      <c r="G223">
         <v>54</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>36</v>
       </c>
-      <c r="N223" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14">
-      <c r="A224" t="s">
+      <c r="O223" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
         <v>458</v>
       </c>
-      <c r="B224">
-        <v>1</v>
-      </c>
-      <c r="C224" t="s">
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224" t="s">
         <v>445</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>459</v>
       </c>
-      <c r="E224" t="s">
-        <v>4</v>
-      </c>
-      <c r="F224">
+      <c r="F224" t="s">
+        <v>4</v>
+      </c>
+      <c r="G224">
         <v>47</v>
       </c>
-      <c r="H224" t="s">
-        <v>10</v>
-      </c>
       <c r="I224" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J224" t="s">
         <v>6</v>
@@ -7087,183 +7760,207 @@
       <c r="K224" t="s">
         <v>6</v>
       </c>
-      <c r="M224" t="s">
+      <c r="L224" t="s">
         <v>6</v>
       </c>
       <c r="N224" t="s">
+        <v>6</v>
+      </c>
+      <c r="O224" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:14">
-      <c r="A225" t="s">
+    <row r="225" spans="1:15">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
         <v>460</v>
       </c>
-      <c r="B225">
-        <v>1</v>
-      </c>
-      <c r="C225" t="s">
+      <c r="C225">
+        <v>1</v>
+      </c>
+      <c r="D225" t="s">
         <v>450</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>461</v>
       </c>
-      <c r="E225" t="s">
-        <v>4</v>
-      </c>
-      <c r="F225">
+      <c r="F225" t="s">
+        <v>4</v>
+      </c>
+      <c r="G225">
         <v>30</v>
       </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>5</v>
       </c>
-      <c r="N225" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14">
-      <c r="A226" t="s">
+      <c r="O225" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
         <v>462</v>
       </c>
-      <c r="B226">
-        <v>1</v>
-      </c>
-      <c r="C226" t="s">
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
         <v>445</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
         <v>463</v>
       </c>
-      <c r="E226" t="s">
-        <v>4</v>
-      </c>
-      <c r="F226">
+      <c r="F226" t="s">
+        <v>4</v>
+      </c>
+      <c r="G226">
         <v>300</v>
       </c>
-      <c r="G226">
-        <v>10</v>
-      </c>
-      <c r="H226" t="s">
+      <c r="H226">
+        <v>10</v>
+      </c>
+      <c r="I226" t="s">
         <v>36</v>
-      </c>
-      <c r="I226" t="s">
-        <v>6</v>
       </c>
       <c r="J226" t="s">
         <v>6</v>
       </c>
       <c r="K226" t="s">
-        <v>31</v>
-      </c>
-      <c r="M226" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="227" spans="1:14">
-      <c r="A227" t="s">
+        <v>6</v>
+      </c>
+      <c r="L226" t="s">
+        <v>31</v>
+      </c>
+      <c r="N226" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
         <v>464</v>
       </c>
-      <c r="B227">
-        <v>1</v>
-      </c>
-      <c r="C227" t="s">
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227" t="s">
         <v>445</v>
       </c>
-      <c r="D227" t="s">
+      <c r="E227" t="s">
         <v>465</v>
       </c>
-      <c r="E227" t="s">
-        <v>4</v>
-      </c>
-      <c r="F227">
+      <c r="F227" t="s">
+        <v>4</v>
+      </c>
+      <c r="G227">
         <v>42</v>
       </c>
-      <c r="G227">
+      <c r="H227">
         <v>15</v>
       </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>36</v>
       </c>
-      <c r="J227" t="s">
+      <c r="K227" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="228" spans="1:14">
-      <c r="A228" t="s">
+    <row r="228" spans="1:15">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
         <v>466</v>
       </c>
-      <c r="B228">
-        <v>1</v>
-      </c>
-      <c r="C228" t="s">
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228" t="s">
         <v>445</v>
       </c>
-      <c r="D228" t="s">
+      <c r="E228" t="s">
         <v>467</v>
       </c>
-      <c r="E228" t="s">
-        <v>4</v>
-      </c>
-      <c r="F228">
+      <c r="F228" t="s">
+        <v>4</v>
+      </c>
+      <c r="G228">
         <v>15</v>
       </c>
-      <c r="H228" t="s">
+      <c r="I228" t="s">
         <v>5</v>
       </c>
-      <c r="N228" t="s">
+      <c r="O228" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:14">
-      <c r="A229" t="s">
+    <row r="229" spans="1:15">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
         <v>468</v>
       </c>
-      <c r="B229">
-        <v>1</v>
-      </c>
-      <c r="C229" t="s">
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229" t="s">
         <v>450</v>
       </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="230" spans="1:14">
-      <c r="A230" t="s">
+    <row r="230" spans="1:15">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
         <v>470</v>
       </c>
-      <c r="B230">
-        <v>1</v>
-      </c>
-      <c r="C230" t="s">
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="D230" t="s">
         <v>445</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>471</v>
       </c>
-      <c r="E230" t="s">
-        <v>4</v>
-      </c>
-      <c r="F230">
+      <c r="F230" t="s">
+        <v>4</v>
+      </c>
+      <c r="G230">
         <v>30</v>
       </c>
-      <c r="H230" t="s">
+      <c r="I230" t="s">
         <v>5</v>
       </c>
-      <c r="N230" t="s">
+      <c r="O230" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:14">
-      <c r="A231" t="s">
+    <row r="231" spans="1:15">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
         <v>472</v>
       </c>
-      <c r="B231">
-        <v>1</v>
-      </c>
-      <c r="C231" t="s">
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231" t="s">
         <v>450</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
         <v>473</v>
       </c>
     </row>

--- a/data/data_shichigawahama_w1.xlsx
+++ b/data/data_shichigawahama_w1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33879256-A346-4A1C-91A5-118F544C697B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CE6D8D-798C-4A9E-A7C1-87F51C96ABCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,10 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="499">
   <si>
-    <t>name</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>岩本松治</t>
   </si>
   <si>
@@ -1676,6 +1672,10 @@
   </si>
   <si>
     <t>id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name_w1</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2029,49 +2029,49 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1" t="s">
         <v>498</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E1" t="s">
         <v>485</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>486</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>487</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>488</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>489</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>490</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>491</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>492</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>493</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>494</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>495</v>
-      </c>
-      <c r="O1" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2079,34 +2079,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>120</v>
       </c>
       <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" t="s">
         <v>6</v>
-      </c>
-      <c r="N2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2114,25 +2114,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2140,28 +2140,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
       <c r="J4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
         <v>6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2169,25 +2169,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2195,22 +2195,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2218,28 +2218,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
         <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2247,25 +2247,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -2273,16 +2273,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2290,25 +2290,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2316,37 +2316,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -2354,16 +2354,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -2371,37 +2371,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
         <v>34</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>35</v>
-      </c>
       <c r="F13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
       <c r="I13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -2409,28 +2409,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
         <v>37</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>38</v>
-      </c>
       <c r="F14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>30</v>
+      </c>
+      <c r="H14">
+        <v>30</v>
+      </c>
+      <c r="I14" t="s">
         <v>4</v>
-      </c>
-      <c r="G14">
-        <v>30</v>
-      </c>
-      <c r="H14">
-        <v>30</v>
-      </c>
-      <c r="I14" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -2438,19 +2438,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
         <v>39</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -2458,22 +2458,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
         <v>41</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>42</v>
-      </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -2481,25 +2481,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
         <v>43</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>44</v>
-      </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -2507,22 +2507,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
         <v>45</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>46</v>
       </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -2530,25 +2530,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" t="s">
         <v>48</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>49</v>
-      </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -2556,31 +2556,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
         <v>50</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" t="s">
-        <v>51</v>
-      </c>
       <c r="F20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>23</v>
       </c>
       <c r="I20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" t="s">
         <v>5</v>
       </c>
-      <c r="K20" t="s">
-        <v>6</v>
-      </c>
       <c r="M20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -2588,34 +2588,34 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>53</v>
-      </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2623,16 +2623,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -2640,25 +2640,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" t="s">
         <v>56</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" t="s">
-        <v>57</v>
-      </c>
       <c r="F23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>30</v>
       </c>
       <c r="I23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -2666,22 +2666,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" t="s">
         <v>58</v>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" t="s">
-        <v>59</v>
-      </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -2689,25 +2689,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" t="s">
         <v>60</v>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" t="s">
-        <v>61</v>
-      </c>
       <c r="F25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25">
         <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -2715,28 +2715,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
         <v>62</v>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" t="s">
-        <v>63</v>
-      </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -2744,31 +2744,31 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
         <v>64</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" t="s">
-        <v>65</v>
-      </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -2776,16 +2776,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -2793,28 +2793,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" t="s">
         <v>68</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" t="s">
-        <v>69</v>
-      </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -2822,16 +2822,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -2839,28 +2839,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="s">
         <v>72</v>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" t="s">
-        <v>73</v>
-      </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -2868,34 +2868,34 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" t="s">
         <v>74</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" t="s">
-        <v>75</v>
-      </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -2903,19 +2903,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" t="s">
         <v>76</v>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" t="s">
-        <v>77</v>
-      </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:15">
@@ -2923,22 +2923,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" t="s">
         <v>78</v>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" t="s">
-        <v>79</v>
-      </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:15">
@@ -2946,37 +2946,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s">
         <v>80</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" t="s">
-        <v>81</v>
-      </c>
       <c r="F35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:15">
@@ -2984,25 +2984,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
         <v>82</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" t="s">
-        <v>83</v>
-      </c>
       <c r="F36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36">
         <v>70</v>
       </c>
       <c r="I36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:15">
@@ -3010,25 +3010,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" t="s">
         <v>84</v>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" t="s">
-        <v>85</v>
-      </c>
       <c r="F37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37">
         <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -3036,37 +3036,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" t="s">
         <v>86</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" t="s">
-        <v>87</v>
-      </c>
       <c r="F38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>40</v>
       </c>
       <c r="I38" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" t="s">
         <v>5</v>
       </c>
-      <c r="J38" t="s">
-        <v>6</v>
-      </c>
       <c r="K38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -3074,22 +3074,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" t="s">
         <v>88</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" t="s">
-        <v>89</v>
-      </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:15">
@@ -3097,25 +3097,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" t="s">
         <v>90</v>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" t="s">
-        <v>91</v>
-      </c>
       <c r="F40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40">
         <v>45</v>
       </c>
       <c r="I40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -3123,19 +3123,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" t="s">
         <v>92</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" t="s">
-        <v>93</v>
-      </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:15">
@@ -3143,16 +3143,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:15">
@@ -3160,16 +3160,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:15">
@@ -3177,22 +3177,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" t="s">
         <v>98</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" t="s">
-        <v>99</v>
-      </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:15">
@@ -3200,25 +3200,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" t="s">
         <v>100</v>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" t="s">
-        <v>101</v>
-      </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:15">
@@ -3226,37 +3226,37 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
         <v>102</v>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" t="s">
-        <v>103</v>
-      </c>
       <c r="F46" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46">
         <v>220</v>
       </c>
       <c r="I46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:15">
@@ -3264,16 +3264,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:15">
@@ -3281,19 +3281,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" t="s">
         <v>106</v>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
-        <v>46</v>
-      </c>
-      <c r="E48" t="s">
-        <v>107</v>
-      </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:15">
@@ -3301,19 +3301,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" t="s">
         <v>108</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" t="s">
-        <v>109</v>
-      </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:15">
@@ -3321,16 +3321,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:15">
@@ -3338,28 +3338,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
         <v>112</v>
       </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>113</v>
       </c>
-      <c r="E51" t="s">
-        <v>114</v>
-      </c>
       <c r="F51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I51" t="s">
         <v>4</v>
       </c>
-      <c r="I51" t="s">
+      <c r="K51" t="s">
         <v>5</v>
       </c>
-      <c r="K51" t="s">
-        <v>6</v>
-      </c>
       <c r="M51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:15">
@@ -3367,22 +3367,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" t="s">
         <v>115</v>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>113</v>
-      </c>
-      <c r="E52" t="s">
-        <v>116</v>
-      </c>
       <c r="F52" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" t="s">
         <v>4</v>
-      </c>
-      <c r="I52" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:15">
@@ -3390,40 +3390,40 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" t="s">
         <v>117</v>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>113</v>
-      </c>
-      <c r="E53" t="s">
-        <v>118</v>
-      </c>
       <c r="F53" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G53">
         <v>82</v>
       </c>
       <c r="I53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:15">
@@ -3431,16 +3431,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" t="s">
         <v>119</v>
-      </c>
-      <c r="E54" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:15">
@@ -3448,25 +3448,25 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" t="s">
         <v>121</v>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E55" t="s">
-        <v>122</v>
-      </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:15">
@@ -3474,28 +3474,28 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" t="s">
         <v>123</v>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="s">
-        <v>119</v>
-      </c>
-      <c r="E56" t="s">
-        <v>124</v>
-      </c>
       <c r="F56" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" t="s">
         <v>4</v>
       </c>
-      <c r="I56" t="s">
-        <v>5</v>
-      </c>
       <c r="K56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:15">
@@ -3503,31 +3503,31 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>112</v>
+      </c>
+      <c r="E57" t="s">
         <v>125</v>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57" t="s">
-        <v>113</v>
-      </c>
-      <c r="E57" t="s">
-        <v>126</v>
-      </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:15">
@@ -3535,22 +3535,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:15">
@@ -3558,19 +3558,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:15">
@@ -3578,28 +3578,28 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>112</v>
+      </c>
+      <c r="E60" t="s">
         <v>129</v>
       </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60" t="s">
-        <v>113</v>
-      </c>
-      <c r="E60" t="s">
-        <v>130</v>
-      </c>
       <c r="F60" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>30</v>
+      </c>
+      <c r="I60" t="s">
         <v>4</v>
       </c>
-      <c r="G60">
-        <v>30</v>
-      </c>
-      <c r="I60" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:15">
@@ -3607,16 +3607,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:15">
@@ -3624,16 +3624,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -3641,25 +3641,25 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
         <v>135</v>
       </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63" t="s">
-        <v>113</v>
-      </c>
-      <c r="E63" t="s">
-        <v>136</v>
-      </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:15">
@@ -3667,22 +3667,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
+        <v>112</v>
+      </c>
+      <c r="E64" t="s">
         <v>137</v>
       </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-      <c r="D64" t="s">
-        <v>113</v>
-      </c>
-      <c r="E64" t="s">
-        <v>138</v>
-      </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:15">
@@ -3690,22 +3690,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65" t="s">
+        <v>112</v>
+      </c>
+      <c r="E65" t="s">
         <v>139</v>
       </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65" t="s">
-        <v>113</v>
-      </c>
-      <c r="E65" t="s">
-        <v>140</v>
-      </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:15">
@@ -3713,19 +3713,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" t="s">
         <v>141</v>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66" t="s">
-        <v>119</v>
-      </c>
-      <c r="E66" t="s">
-        <v>142</v>
-      </c>
       <c r="F66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66">
         <v>34</v>
@@ -3734,19 +3734,19 @@
         <v>3</v>
       </c>
       <c r="I66" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -3754,16 +3754,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E67" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:15">
@@ -3771,37 +3771,37 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68" t="s">
         <v>145</v>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68" t="s">
-        <v>113</v>
-      </c>
-      <c r="E68" t="s">
-        <v>146</v>
-      </c>
       <c r="F68" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68">
         <v>28</v>
       </c>
       <c r="I68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -3809,22 +3809,22 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>112</v>
+      </c>
+      <c r="E69" t="s">
         <v>147</v>
       </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69" t="s">
-        <v>113</v>
-      </c>
-      <c r="E69" t="s">
-        <v>148</v>
-      </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:15">
@@ -3832,22 +3832,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>112</v>
+      </c>
+      <c r="E70" t="s">
         <v>149</v>
       </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70" t="s">
-        <v>113</v>
-      </c>
-      <c r="E70" t="s">
-        <v>150</v>
-      </c>
       <c r="F70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:15">
@@ -3855,31 +3855,31 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="s">
+        <v>112</v>
+      </c>
+      <c r="E71" t="s">
         <v>151</v>
       </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71" t="s">
-        <v>113</v>
-      </c>
-      <c r="E71" t="s">
-        <v>152</v>
-      </c>
       <c r="F71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:15">
@@ -3887,19 +3887,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>112</v>
+      </c>
+      <c r="E72" t="s">
         <v>153</v>
       </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72" t="s">
-        <v>113</v>
-      </c>
-      <c r="E72" t="s">
-        <v>154</v>
-      </c>
       <c r="F72" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72">
         <v>35</v>
@@ -3908,13 +3908,13 @@
         <v>7</v>
       </c>
       <c r="I72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:15">
@@ -3922,16 +3922,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E73" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:15">
@@ -3939,22 +3939,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
+        <v>112</v>
+      </c>
+      <c r="E74" t="s">
         <v>157</v>
       </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74" t="s">
-        <v>113</v>
-      </c>
-      <c r="E74" t="s">
-        <v>158</v>
-      </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:15">
@@ -3962,16 +3962,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E75" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:15">
@@ -3979,16 +3979,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:15">
@@ -3996,25 +3996,25 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>112</v>
+      </c>
+      <c r="E77" t="s">
         <v>163</v>
       </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77" t="s">
-        <v>113</v>
-      </c>
-      <c r="E77" t="s">
-        <v>164</v>
-      </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:15">
@@ -4022,19 +4022,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78" t="s">
+        <v>112</v>
+      </c>
+      <c r="E78" t="s">
         <v>165</v>
       </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78" t="s">
-        <v>113</v>
-      </c>
-      <c r="E78" t="s">
-        <v>166</v>
-      </c>
       <c r="F78" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78">
         <v>140</v>
@@ -4043,22 +4043,22 @@
         <v>15</v>
       </c>
       <c r="I78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:15">
@@ -4066,28 +4066,28 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
+        <v>112</v>
+      </c>
+      <c r="E79" t="s">
         <v>167</v>
       </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79" t="s">
-        <v>113</v>
-      </c>
-      <c r="E79" t="s">
-        <v>168</v>
-      </c>
       <c r="F79" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79">
         <v>6</v>
       </c>
       <c r="I79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:15">
@@ -4095,22 +4095,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>112</v>
+      </c>
+      <c r="E80" t="s">
         <v>169</v>
       </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80" t="s">
-        <v>113</v>
-      </c>
-      <c r="E80" t="s">
-        <v>170</v>
-      </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:15">
@@ -4118,16 +4118,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:15">
@@ -4135,28 +4135,28 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>112</v>
+      </c>
+      <c r="E82" t="s">
         <v>173</v>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
-        <v>113</v>
-      </c>
-      <c r="E82" t="s">
-        <v>174</v>
-      </c>
       <c r="F82" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82">
         <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:15">
@@ -4164,22 +4164,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>174</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83" t="s">
         <v>175</v>
       </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83" t="s">
-        <v>113</v>
-      </c>
-      <c r="E83" t="s">
-        <v>176</v>
-      </c>
       <c r="F83" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I83" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:15">
@@ -4187,28 +4187,28 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>176</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
+        <v>118</v>
+      </c>
+      <c r="E84" t="s">
         <v>177</v>
       </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84" t="s">
-        <v>119</v>
-      </c>
-      <c r="E84" t="s">
-        <v>178</v>
-      </c>
       <c r="F84" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G84">
         <v>11</v>
       </c>
       <c r="I84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:15">
@@ -4216,22 +4216,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" t="s">
         <v>179</v>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85" t="s">
-        <v>119</v>
-      </c>
-      <c r="E85" t="s">
-        <v>180</v>
-      </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:15">
@@ -4239,28 +4239,28 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F86" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G86">
         <v>9</v>
       </c>
       <c r="I86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:15">
@@ -4268,37 +4268,37 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>181</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
+        <v>112</v>
+      </c>
+      <c r="E87" t="s">
         <v>182</v>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87" t="s">
-        <v>113</v>
-      </c>
-      <c r="E87" t="s">
-        <v>183</v>
-      </c>
       <c r="F87" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:15">
@@ -4306,31 +4306,31 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>112</v>
+      </c>
+      <c r="E88" t="s">
         <v>184</v>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88" t="s">
-        <v>113</v>
-      </c>
-      <c r="E88" t="s">
-        <v>185</v>
-      </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:15">
@@ -4338,37 +4338,37 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
+        <v>112</v>
+      </c>
+      <c r="E89" t="s">
         <v>186</v>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89" t="s">
-        <v>113</v>
-      </c>
-      <c r="E89" t="s">
-        <v>187</v>
-      </c>
       <c r="F89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:15">
@@ -4376,16 +4376,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E90" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:15">
@@ -4393,31 +4393,31 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
+        <v>112</v>
+      </c>
+      <c r="E91" t="s">
         <v>190</v>
       </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91" t="s">
-        <v>113</v>
-      </c>
-      <c r="E91" t="s">
-        <v>191</v>
-      </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:15">
@@ -4425,22 +4425,22 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>191</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>112</v>
+      </c>
+      <c r="E92" t="s">
         <v>192</v>
       </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92" t="s">
-        <v>113</v>
-      </c>
-      <c r="E92" t="s">
-        <v>193</v>
-      </c>
       <c r="F92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:15">
@@ -4448,25 +4448,25 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>193</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>118</v>
+      </c>
+      <c r="E93" t="s">
         <v>194</v>
       </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
-      <c r="D93" t="s">
-        <v>119</v>
-      </c>
-      <c r="E93" t="s">
-        <v>195</v>
-      </c>
       <c r="F93" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G93">
         <v>43</v>
       </c>
       <c r="I93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:15">
@@ -4474,19 +4474,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>195</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94" t="s">
+        <v>112</v>
+      </c>
+      <c r="E94" t="s">
         <v>196</v>
       </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94" t="s">
-        <v>113</v>
-      </c>
-      <c r="E94" t="s">
-        <v>197</v>
-      </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G94">
         <v>30</v>
@@ -4495,19 +4495,19 @@
         <v>10</v>
       </c>
       <c r="I94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:15">
@@ -4515,31 +4515,31 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>197</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95" t="s">
         <v>198</v>
       </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95" t="s">
-        <v>113</v>
-      </c>
-      <c r="E95" t="s">
-        <v>199</v>
-      </c>
       <c r="F95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:15">
@@ -4547,19 +4547,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>199</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96" t="s">
+        <v>112</v>
+      </c>
+      <c r="E96" t="s">
         <v>200</v>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96" t="s">
-        <v>113</v>
-      </c>
-      <c r="E96" t="s">
-        <v>201</v>
-      </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:15">
@@ -4567,16 +4567,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E97" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="98" spans="1:15">
@@ -4584,25 +4584,25 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>203</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="s">
+        <v>112</v>
+      </c>
+      <c r="E98" t="s">
         <v>204</v>
       </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-      <c r="D98" t="s">
-        <v>113</v>
-      </c>
-      <c r="E98" t="s">
-        <v>205</v>
-      </c>
       <c r="F98" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G98">
         <v>115</v>
       </c>
       <c r="I98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:15">
@@ -4610,22 +4610,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>205</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>112</v>
+      </c>
+      <c r="E99" t="s">
         <v>206</v>
       </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99" t="s">
-        <v>113</v>
-      </c>
-      <c r="E99" t="s">
-        <v>207</v>
-      </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O99" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:15">
@@ -4633,16 +4633,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E100" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:15">
@@ -4650,25 +4650,25 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>209</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
         <v>210</v>
       </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>211</v>
       </c>
-      <c r="E101" t="s">
-        <v>212</v>
-      </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:15">
@@ -4676,16 +4676,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102" t="s">
+        <v>212</v>
+      </c>
+      <c r="E102" t="s">
         <v>213</v>
-      </c>
-      <c r="E102" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="103" spans="1:15">
@@ -4693,16 +4693,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E103" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:15">
@@ -4710,16 +4710,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E104" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:15">
@@ -4727,25 +4727,25 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>218</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
+        <v>210</v>
+      </c>
+      <c r="E105" t="s">
         <v>219</v>
       </c>
-      <c r="C105">
-        <v>1</v>
-      </c>
-      <c r="D105" t="s">
-        <v>211</v>
-      </c>
-      <c r="E105" t="s">
-        <v>220</v>
-      </c>
       <c r="F105" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G105">
         <v>50</v>
       </c>
       <c r="I105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:15">
@@ -4753,22 +4753,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>220</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>212</v>
+      </c>
+      <c r="E106" t="s">
         <v>221</v>
       </c>
-      <c r="C106">
-        <v>1</v>
-      </c>
-      <c r="D106" t="s">
-        <v>213</v>
-      </c>
-      <c r="E106" t="s">
-        <v>222</v>
-      </c>
       <c r="F106" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:15">
@@ -4776,22 +4776,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C107">
         <v>1</v>
       </c>
       <c r="D107" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F107" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:15">
@@ -4799,16 +4799,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="109" spans="1:15">
@@ -4816,16 +4816,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E109" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="110" spans="1:15">
@@ -4833,22 +4833,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>226</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="s">
+        <v>212</v>
+      </c>
+      <c r="E110" t="s">
         <v>227</v>
       </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110" t="s">
-        <v>213</v>
-      </c>
-      <c r="E110" t="s">
-        <v>228</v>
-      </c>
       <c r="F110" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O110" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:15">
@@ -4856,34 +4856,34 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>228</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111" t="s">
+        <v>210</v>
+      </c>
+      <c r="E111" t="s">
         <v>229</v>
       </c>
-      <c r="C111">
-        <v>1</v>
-      </c>
-      <c r="D111" t="s">
-        <v>211</v>
-      </c>
-      <c r="E111" t="s">
-        <v>230</v>
-      </c>
       <c r="F111" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:15">
@@ -4891,22 +4891,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C112">
         <v>1</v>
       </c>
       <c r="D112" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E112" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F112" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O112" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:15">
@@ -4914,16 +4914,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E113" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" spans="1:15">
@@ -4931,16 +4931,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E114" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:15">
@@ -4948,16 +4948,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E115" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="116" spans="1:15">
@@ -4965,22 +4965,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>237</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
+        <v>210</v>
+      </c>
+      <c r="E116" t="s">
         <v>238</v>
       </c>
-      <c r="C116">
-        <v>1</v>
-      </c>
-      <c r="D116" t="s">
-        <v>211</v>
-      </c>
-      <c r="E116" t="s">
-        <v>239</v>
-      </c>
       <c r="F116" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:15">
@@ -4988,22 +4988,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E117" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F117" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O117" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:15">
@@ -5011,22 +5011,22 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>240</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>212</v>
+      </c>
+      <c r="E118" t="s">
         <v>241</v>
       </c>
-      <c r="C118">
-        <v>1</v>
-      </c>
-      <c r="D118" t="s">
-        <v>213</v>
-      </c>
-      <c r="E118" t="s">
-        <v>242</v>
-      </c>
       <c r="F118" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O118" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:15">
@@ -5034,16 +5034,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E119" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="120" spans="1:15">
@@ -5051,16 +5051,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E120" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="121" spans="1:15">
@@ -5068,16 +5068,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E121" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="122" spans="1:15">
@@ -5085,31 +5085,31 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
+        <v>247</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="s">
+        <v>210</v>
+      </c>
+      <c r="E122" t="s">
         <v>248</v>
       </c>
-      <c r="C122">
-        <v>1</v>
-      </c>
-      <c r="D122" t="s">
-        <v>211</v>
-      </c>
-      <c r="E122" t="s">
-        <v>249</v>
-      </c>
       <c r="F122" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G122">
         <v>140</v>
       </c>
       <c r="I122" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:15">
@@ -5117,16 +5117,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E123" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124" spans="1:15">
@@ -5134,16 +5134,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E124" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="125" spans="1:15">
@@ -5151,16 +5151,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C125">
         <v>0</v>
       </c>
       <c r="D125" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E125" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:15">
@@ -5168,16 +5168,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E126" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" spans="1:15">
@@ -5185,22 +5185,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
+        <v>257</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127" t="s">
+        <v>210</v>
+      </c>
+      <c r="E127" t="s">
         <v>258</v>
       </c>
-      <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="D127" t="s">
-        <v>211</v>
-      </c>
-      <c r="E127" t="s">
-        <v>259</v>
-      </c>
       <c r="F127" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O127" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:15">
@@ -5208,19 +5208,19 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>259</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128" t="s">
+        <v>210</v>
+      </c>
+      <c r="E128" t="s">
         <v>260</v>
       </c>
-      <c r="C128">
-        <v>1</v>
-      </c>
-      <c r="D128" t="s">
-        <v>211</v>
-      </c>
-      <c r="E128" t="s">
-        <v>261</v>
-      </c>
       <c r="F128" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G128">
         <v>80</v>
@@ -5229,19 +5229,19 @@
         <v>30</v>
       </c>
       <c r="I128" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:15">
@@ -5249,19 +5249,19 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
+        <v>261</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129" t="s">
+        <v>210</v>
+      </c>
+      <c r="E129" t="s">
         <v>262</v>
       </c>
-      <c r="C129">
-        <v>1</v>
-      </c>
-      <c r="D129" t="s">
-        <v>211</v>
-      </c>
-      <c r="E129" t="s">
-        <v>263</v>
-      </c>
       <c r="F129" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:15">
@@ -5269,16 +5269,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C130">
         <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E130" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" spans="1:15">
@@ -5286,31 +5286,31 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131" t="s">
         <v>266</v>
       </c>
-      <c r="C131">
-        <v>1</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>267</v>
       </c>
-      <c r="E131" t="s">
-        <v>268</v>
-      </c>
       <c r="F131" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G131">
         <v>110</v>
       </c>
       <c r="I131" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:15">
@@ -5318,16 +5318,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E132" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:15">
@@ -5335,16 +5335,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:15">
@@ -5352,16 +5352,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C134">
         <v>0</v>
       </c>
       <c r="D134" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E134" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="135" spans="1:15">
@@ -5369,16 +5369,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E135" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="136" spans="1:15">
@@ -5386,37 +5386,37 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
+        <v>277</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136" t="s">
         <v>278</v>
       </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
         <v>279</v>
       </c>
-      <c r="E136" t="s">
-        <v>280</v>
-      </c>
       <c r="F136" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I136" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N136" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O136" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:15">
@@ -5424,25 +5424,25 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
+        <v>280</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="s">
+        <v>266</v>
+      </c>
+      <c r="E137" t="s">
         <v>281</v>
       </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-      <c r="D137" t="s">
-        <v>267</v>
-      </c>
-      <c r="E137" t="s">
-        <v>282</v>
-      </c>
       <c r="F137" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G137">
         <v>13</v>
       </c>
       <c r="I137" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:15">
@@ -5450,25 +5450,25 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
+        <v>282</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138" t="s">
+        <v>266</v>
+      </c>
+      <c r="E138" t="s">
         <v>283</v>
       </c>
-      <c r="C138">
-        <v>1</v>
-      </c>
-      <c r="D138" t="s">
-        <v>267</v>
-      </c>
-      <c r="E138" t="s">
-        <v>284</v>
-      </c>
       <c r="F138" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I138" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O138" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:15">
@@ -5476,19 +5476,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
+        <v>284</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139" t="s">
+        <v>266</v>
+      </c>
+      <c r="E139" t="s">
         <v>285</v>
       </c>
-      <c r="C139">
-        <v>1</v>
-      </c>
-      <c r="D139" t="s">
-        <v>267</v>
-      </c>
-      <c r="E139" t="s">
-        <v>286</v>
-      </c>
       <c r="F139" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G139">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>29</v>
       </c>
       <c r="I139" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:15">
@@ -5505,40 +5505,40 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
+        <v>286</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" t="s">
+        <v>266</v>
+      </c>
+      <c r="E140" t="s">
         <v>287</v>
       </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="D140" t="s">
-        <v>267</v>
-      </c>
-      <c r="E140" t="s">
-        <v>288</v>
-      </c>
       <c r="F140" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G140">
         <v>267</v>
       </c>
       <c r="I140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J140" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K140" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L140" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N140" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O140" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:15">
@@ -5546,16 +5546,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E141" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="142" spans="1:15">
@@ -5563,16 +5563,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C142">
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E142" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="143" spans="1:15">
@@ -5580,19 +5580,19 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>292</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="s">
+        <v>266</v>
+      </c>
+      <c r="E143" t="s">
         <v>293</v>
       </c>
-      <c r="C143">
-        <v>1</v>
-      </c>
-      <c r="D143" t="s">
-        <v>267</v>
-      </c>
-      <c r="E143" t="s">
-        <v>294</v>
-      </c>
       <c r="F143" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G143">
         <v>89</v>
@@ -5601,19 +5601,19 @@
         <v>10</v>
       </c>
       <c r="I143" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K143" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L143" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N143" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:15">
@@ -5621,16 +5621,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E144" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="145" spans="1:15">
@@ -5638,16 +5638,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C145">
         <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E145" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="146" spans="1:15">
@@ -5655,16 +5655,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C146">
         <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E146" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="147" spans="1:15">
@@ -5672,25 +5672,25 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
+        <v>300</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
+        <v>266</v>
+      </c>
+      <c r="E147" t="s">
         <v>301</v>
       </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147" t="s">
-        <v>267</v>
-      </c>
-      <c r="E147" t="s">
-        <v>302</v>
-      </c>
       <c r="F147" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G147">
         <v>110</v>
       </c>
       <c r="I147" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:15">
@@ -5698,25 +5698,25 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E148" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F148" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O148" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:15">
@@ -5724,22 +5724,22 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
+        <v>303</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149" t="s">
+        <v>266</v>
+      </c>
+      <c r="E149" t="s">
         <v>304</v>
       </c>
-      <c r="C149">
-        <v>1</v>
-      </c>
-      <c r="D149" t="s">
-        <v>267</v>
-      </c>
-      <c r="E149" t="s">
-        <v>305</v>
-      </c>
       <c r="F149" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O149" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" spans="1:15">
@@ -5747,16 +5747,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C150">
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E150" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="151" spans="1:15">
@@ -5764,16 +5764,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E151" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="152" spans="1:15">
@@ -5781,28 +5781,28 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
+        <v>309</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
+        <v>266</v>
+      </c>
+      <c r="E152" t="s">
         <v>310</v>
       </c>
-      <c r="C152">
-        <v>1</v>
-      </c>
-      <c r="D152" t="s">
-        <v>267</v>
-      </c>
-      <c r="E152" t="s">
-        <v>311</v>
-      </c>
       <c r="F152" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G152">
         <v>40</v>
       </c>
       <c r="I152" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O152" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:15">
@@ -5810,25 +5810,25 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
+        <v>311</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153" t="s">
+        <v>266</v>
+      </c>
+      <c r="E153" t="s">
         <v>312</v>
       </c>
-      <c r="C153">
-        <v>1</v>
-      </c>
-      <c r="D153" t="s">
-        <v>267</v>
-      </c>
-      <c r="E153" t="s">
-        <v>313</v>
-      </c>
       <c r="F153" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I153" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O153" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" spans="1:15">
@@ -5836,16 +5836,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C154">
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E154" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="155" spans="1:15">
@@ -5853,16 +5853,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E155" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="156" spans="1:15">
@@ -5870,19 +5870,19 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>317</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156" t="s">
+        <v>266</v>
+      </c>
+      <c r="E156" t="s">
         <v>318</v>
       </c>
-      <c r="C156">
-        <v>1</v>
-      </c>
-      <c r="D156" t="s">
-        <v>267</v>
-      </c>
-      <c r="E156" t="s">
-        <v>319</v>
-      </c>
       <c r="F156" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G156">
         <v>82</v>
@@ -5891,22 +5891,22 @@
         <v>50</v>
       </c>
       <c r="I156" t="s">
+        <v>4</v>
+      </c>
+      <c r="J156" t="s">
+        <v>30</v>
+      </c>
+      <c r="K156" t="s">
         <v>5</v>
       </c>
-      <c r="J156" t="s">
-        <v>31</v>
-      </c>
-      <c r="K156" t="s">
-        <v>6</v>
-      </c>
       <c r="L156" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M156" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N156" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:15">
@@ -5914,16 +5914,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E157" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" spans="1:15">
@@ -5931,37 +5931,37 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>321</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158" t="s">
+        <v>266</v>
+      </c>
+      <c r="E158" t="s">
         <v>322</v>
       </c>
-      <c r="C158">
-        <v>1</v>
-      </c>
-      <c r="D158" t="s">
-        <v>267</v>
-      </c>
-      <c r="E158" t="s">
-        <v>323</v>
-      </c>
       <c r="F158" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G158">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J158" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K158" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L158" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N158" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:15">
@@ -5969,25 +5969,25 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>323</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159" t="s">
+        <v>266</v>
+      </c>
+      <c r="E159" t="s">
         <v>324</v>
       </c>
-      <c r="C159">
-        <v>1</v>
-      </c>
-      <c r="D159" t="s">
-        <v>267</v>
-      </c>
-      <c r="E159" t="s">
-        <v>325</v>
-      </c>
       <c r="F159" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I159" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O159" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" spans="1:15">
@@ -5995,19 +5995,19 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>325</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160" t="s">
+        <v>266</v>
+      </c>
+      <c r="E160" t="s">
         <v>326</v>
       </c>
-      <c r="C160">
-        <v>1</v>
-      </c>
-      <c r="D160" t="s">
-        <v>267</v>
-      </c>
-      <c r="E160" t="s">
-        <v>327</v>
-      </c>
       <c r="F160" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G160">
         <v>55</v>
@@ -6016,16 +6016,16 @@
         <v>8</v>
       </c>
       <c r="I160" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J160" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K160" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:15">
@@ -6033,16 +6033,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C161">
         <v>0</v>
       </c>
       <c r="D161" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E161" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="162" spans="1:15">
@@ -6050,16 +6050,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C162">
         <v>0</v>
       </c>
       <c r="D162" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E162" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="163" spans="1:15">
@@ -6067,34 +6067,34 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
+        <v>331</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
         <v>332</v>
       </c>
-      <c r="C163">
-        <v>1</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>333</v>
       </c>
-      <c r="E163" t="s">
-        <v>334</v>
-      </c>
       <c r="F163" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I163" t="s">
+        <v>4</v>
+      </c>
+      <c r="J163" t="s">
         <v>5</v>
       </c>
-      <c r="J163" t="s">
+      <c r="K163" t="s">
+        <v>5</v>
+      </c>
+      <c r="M163" t="s">
+        <v>5</v>
+      </c>
+      <c r="O163" t="s">
         <v>6</v>
-      </c>
-      <c r="K163" t="s">
-        <v>6</v>
-      </c>
-      <c r="M163" t="s">
-        <v>6</v>
-      </c>
-      <c r="O163" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:15">
@@ -6102,28 +6102,28 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
+        <v>334</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164" t="s">
         <v>335</v>
       </c>
-      <c r="C164">
-        <v>1</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>336</v>
       </c>
-      <c r="E164" t="s">
-        <v>337</v>
-      </c>
       <c r="F164" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G164">
         <v>37</v>
       </c>
       <c r="I164" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O164" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165" spans="1:15">
@@ -6131,25 +6131,25 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
+        <v>337</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165" t="s">
+        <v>332</v>
+      </c>
+      <c r="E165" t="s">
         <v>338</v>
       </c>
-      <c r="C165">
-        <v>1</v>
-      </c>
-      <c r="D165" t="s">
-        <v>333</v>
-      </c>
-      <c r="E165" t="s">
-        <v>339</v>
-      </c>
       <c r="F165" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J165" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K165" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:15">
@@ -6157,25 +6157,25 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>339</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166" t="s">
+        <v>332</v>
+      </c>
+      <c r="E166" t="s">
         <v>340</v>
       </c>
-      <c r="C166">
-        <v>1</v>
-      </c>
-      <c r="D166" t="s">
-        <v>333</v>
-      </c>
-      <c r="E166" t="s">
-        <v>341</v>
-      </c>
       <c r="F166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K166" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O166" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" spans="1:15">
@@ -6183,37 +6183,37 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>341</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" t="s">
+        <v>332</v>
+      </c>
+      <c r="E167" t="s">
         <v>342</v>
       </c>
-      <c r="C167">
-        <v>1</v>
-      </c>
-      <c r="D167" t="s">
-        <v>333</v>
-      </c>
-      <c r="E167" t="s">
-        <v>343</v>
-      </c>
       <c r="F167" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G167">
         <v>15</v>
       </c>
       <c r="I167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J167" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K167" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M167" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:15">
@@ -6221,16 +6221,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C168">
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E168" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="169" spans="1:15">
@@ -6238,25 +6238,25 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
+        <v>345</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169" t="s">
+        <v>332</v>
+      </c>
+      <c r="E169" t="s">
         <v>346</v>
       </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-      <c r="D169" t="s">
-        <v>333</v>
-      </c>
-      <c r="E169" t="s">
-        <v>347</v>
-      </c>
       <c r="F169" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J169" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L169" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:15">
@@ -6264,16 +6264,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C170">
         <v>0</v>
       </c>
       <c r="D170" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E170" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="171" spans="1:15">
@@ -6281,34 +6281,34 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
+        <v>349</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" t="s">
+        <v>332</v>
+      </c>
+      <c r="E171" t="s">
         <v>350</v>
       </c>
-      <c r="C171">
-        <v>1</v>
-      </c>
-      <c r="D171" t="s">
-        <v>333</v>
-      </c>
-      <c r="E171" t="s">
-        <v>351</v>
-      </c>
       <c r="F171" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J171" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K171" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L171" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:15">
@@ -6316,28 +6316,28 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
+        <v>351</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172" t="s">
+        <v>332</v>
+      </c>
+      <c r="E172" t="s">
         <v>352</v>
       </c>
-      <c r="C172">
-        <v>1</v>
-      </c>
-      <c r="D172" t="s">
-        <v>333</v>
-      </c>
-      <c r="E172" t="s">
-        <v>353</v>
-      </c>
       <c r="F172" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G172">
         <v>68</v>
       </c>
       <c r="I172" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O172" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:15">
@@ -6345,19 +6345,19 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>353</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" t="s">
+        <v>332</v>
+      </c>
+      <c r="E173" t="s">
         <v>354</v>
       </c>
-      <c r="C173">
-        <v>1</v>
-      </c>
-      <c r="D173" t="s">
-        <v>333</v>
-      </c>
-      <c r="E173" t="s">
-        <v>355</v>
-      </c>
       <c r="F173" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:15">
@@ -6365,25 +6365,25 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>355</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="D174" t="s">
+        <v>332</v>
+      </c>
+      <c r="E174" t="s">
         <v>356</v>
       </c>
-      <c r="C174">
-        <v>1</v>
-      </c>
-      <c r="D174" t="s">
-        <v>333</v>
-      </c>
-      <c r="E174" t="s">
-        <v>357</v>
-      </c>
       <c r="F174" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J174" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K174" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:15">
@@ -6391,28 +6391,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>357</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175" t="s">
+        <v>332</v>
+      </c>
+      <c r="E175" t="s">
         <v>358</v>
       </c>
-      <c r="C175">
-        <v>1</v>
-      </c>
-      <c r="D175" t="s">
-        <v>333</v>
-      </c>
-      <c r="E175" t="s">
-        <v>359</v>
-      </c>
       <c r="F175" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J175" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K175" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O175" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:15">
@@ -6420,28 +6420,28 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>359</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176" t="s">
+        <v>335</v>
+      </c>
+      <c r="E176" t="s">
         <v>360</v>
       </c>
-      <c r="C176">
-        <v>1</v>
-      </c>
-      <c r="D176" t="s">
-        <v>336</v>
-      </c>
-      <c r="E176" t="s">
-        <v>361</v>
-      </c>
       <c r="F176" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G176">
         <v>20</v>
       </c>
       <c r="I176" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O176" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:15">
@@ -6449,16 +6449,16 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C177">
         <v>0</v>
       </c>
       <c r="D177" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E177" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="178" spans="1:15">
@@ -6466,25 +6466,25 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>363</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178" t="s">
+        <v>332</v>
+      </c>
+      <c r="E178" t="s">
         <v>364</v>
       </c>
-      <c r="C178">
-        <v>1</v>
-      </c>
-      <c r="D178" t="s">
-        <v>333</v>
-      </c>
-      <c r="E178" t="s">
-        <v>365</v>
-      </c>
       <c r="F178" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I178" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O178" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:15">
@@ -6492,34 +6492,34 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E179" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F179" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I179" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:15">
@@ -6527,28 +6527,28 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
+        <v>366</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180" t="s">
+        <v>332</v>
+      </c>
+      <c r="E180" t="s">
         <v>367</v>
       </c>
-      <c r="C180">
-        <v>1</v>
-      </c>
-      <c r="D180" t="s">
-        <v>333</v>
-      </c>
-      <c r="E180" t="s">
-        <v>368</v>
-      </c>
       <c r="F180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J180" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M180" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O180" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" spans="1:15">
@@ -6556,25 +6556,25 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>368</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181" t="s">
+        <v>332</v>
+      </c>
+      <c r="E181" t="s">
         <v>369</v>
       </c>
-      <c r="C181">
-        <v>1</v>
-      </c>
-      <c r="D181" t="s">
-        <v>333</v>
-      </c>
-      <c r="E181" t="s">
-        <v>370</v>
-      </c>
       <c r="F181" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J181" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O181" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:15">
@@ -6582,34 +6582,34 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>370</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182" t="s">
+        <v>332</v>
+      </c>
+      <c r="E182" t="s">
         <v>371</v>
       </c>
-      <c r="C182">
-        <v>1</v>
-      </c>
-      <c r="D182" t="s">
-        <v>333</v>
-      </c>
-      <c r="E182" t="s">
-        <v>372</v>
-      </c>
       <c r="F182" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G182">
         <v>22</v>
       </c>
       <c r="I182" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J182" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K182" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O182" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:15">
@@ -6617,34 +6617,34 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
+        <v>372</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183" t="s">
+        <v>332</v>
+      </c>
+      <c r="E183" t="s">
         <v>373</v>
       </c>
-      <c r="C183">
-        <v>1</v>
-      </c>
-      <c r="D183" t="s">
-        <v>333</v>
-      </c>
-      <c r="E183" t="s">
-        <v>374</v>
-      </c>
       <c r="F183" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G183">
         <v>35</v>
       </c>
       <c r="I183" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J183" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K183" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M183" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184" spans="1:15">
@@ -6652,16 +6652,16 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C184">
         <v>0</v>
       </c>
       <c r="D184" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E184" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:15">
@@ -6669,28 +6669,28 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
+        <v>376</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185" t="s">
+        <v>335</v>
+      </c>
+      <c r="E185" t="s">
         <v>377</v>
       </c>
-      <c r="C185">
-        <v>1</v>
-      </c>
-      <c r="D185" t="s">
-        <v>336</v>
-      </c>
-      <c r="E185" t="s">
-        <v>378</v>
-      </c>
       <c r="F185" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G185">
         <v>15</v>
       </c>
       <c r="I185" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O185" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:15">
@@ -6698,28 +6698,28 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>378</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="s">
+        <v>332</v>
+      </c>
+      <c r="E186" t="s">
         <v>379</v>
       </c>
-      <c r="C186">
-        <v>1</v>
-      </c>
-      <c r="D186" t="s">
-        <v>333</v>
-      </c>
-      <c r="E186" t="s">
-        <v>380</v>
-      </c>
       <c r="F186" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I186" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J186" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M186" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:15">
@@ -6727,37 +6727,37 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>380</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="s">
+        <v>332</v>
+      </c>
+      <c r="E187" t="s">
         <v>381</v>
       </c>
-      <c r="C187">
-        <v>1</v>
-      </c>
-      <c r="D187" t="s">
-        <v>333</v>
-      </c>
-      <c r="E187" t="s">
-        <v>382</v>
-      </c>
       <c r="F187" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I187" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O187" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:15">
@@ -6765,28 +6765,28 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>382</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>335</v>
+      </c>
+      <c r="E188" t="s">
         <v>383</v>
       </c>
-      <c r="C188">
-        <v>1</v>
-      </c>
-      <c r="D188" t="s">
-        <v>336</v>
-      </c>
-      <c r="E188" t="s">
-        <v>384</v>
-      </c>
       <c r="F188" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G188">
         <v>13</v>
       </c>
       <c r="I188" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O188" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:15">
@@ -6794,28 +6794,28 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>384</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189" t="s">
+        <v>335</v>
+      </c>
+      <c r="E189" t="s">
         <v>385</v>
       </c>
-      <c r="C189">
-        <v>1</v>
-      </c>
-      <c r="D189" t="s">
-        <v>336</v>
-      </c>
-      <c r="E189" t="s">
-        <v>386</v>
-      </c>
       <c r="F189" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G189">
         <v>12</v>
       </c>
       <c r="I189" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O189" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:15">
@@ -6823,31 +6823,31 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
+        <v>386</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190" t="s">
+        <v>332</v>
+      </c>
+      <c r="E190" t="s">
         <v>387</v>
       </c>
-      <c r="C190">
-        <v>1</v>
-      </c>
-      <c r="D190" t="s">
-        <v>333</v>
-      </c>
-      <c r="E190" t="s">
-        <v>388</v>
-      </c>
       <c r="F190" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I190" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191" spans="1:15">
@@ -6855,31 +6855,31 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>388</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191" t="s">
+        <v>332</v>
+      </c>
+      <c r="E191" t="s">
         <v>389</v>
       </c>
-      <c r="C191">
-        <v>1</v>
-      </c>
-      <c r="D191" t="s">
-        <v>333</v>
-      </c>
-      <c r="E191" t="s">
-        <v>390</v>
-      </c>
       <c r="F191" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I191" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J191" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K191" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O191" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:15">
@@ -6887,34 +6887,34 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>390</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="s">
+        <v>332</v>
+      </c>
+      <c r="E192" t="s">
         <v>391</v>
       </c>
-      <c r="C192">
-        <v>1</v>
-      </c>
-      <c r="D192" t="s">
-        <v>333</v>
-      </c>
-      <c r="E192" t="s">
-        <v>392</v>
-      </c>
       <c r="F192" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="193" spans="1:15">
@@ -6922,25 +6922,25 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>392</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193" t="s">
+        <v>332</v>
+      </c>
+      <c r="E193" t="s">
         <v>393</v>
       </c>
-      <c r="C193">
-        <v>1</v>
-      </c>
-      <c r="D193" t="s">
-        <v>333</v>
-      </c>
-      <c r="E193" t="s">
-        <v>394</v>
-      </c>
       <c r="F193" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I193" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O193" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" spans="1:15">
@@ -6948,22 +6948,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>394</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>332</v>
+      </c>
+      <c r="E194" t="s">
         <v>395</v>
       </c>
-      <c r="C194">
-        <v>1</v>
-      </c>
-      <c r="D194" t="s">
-        <v>333</v>
-      </c>
-      <c r="E194" t="s">
-        <v>396</v>
-      </c>
       <c r="F194" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I194" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:15">
@@ -6971,16 +6971,16 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C195">
         <v>0</v>
       </c>
       <c r="D195" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E195" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="196" spans="1:15">
@@ -6988,16 +6988,16 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196" t="s">
+        <v>399</v>
+      </c>
+      <c r="E196" t="s">
         <v>400</v>
-      </c>
-      <c r="E196" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="197" spans="1:15">
@@ -7005,19 +7005,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>401</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="s">
+        <v>399</v>
+      </c>
+      <c r="E197" t="s">
         <v>402</v>
       </c>
-      <c r="C197">
-        <v>1</v>
-      </c>
-      <c r="D197" t="s">
-        <v>400</v>
-      </c>
-      <c r="E197" t="s">
-        <v>403</v>
-      </c>
       <c r="F197" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G197">
         <v>25</v>
@@ -7026,19 +7026,19 @@
         <v>10</v>
       </c>
       <c r="I197" t="s">
+        <v>4</v>
+      </c>
+      <c r="J197" t="s">
         <v>5</v>
       </c>
-      <c r="J197" t="s">
+      <c r="K197" t="s">
+        <v>5</v>
+      </c>
+      <c r="M197" t="s">
+        <v>5</v>
+      </c>
+      <c r="O197" t="s">
         <v>6</v>
-      </c>
-      <c r="K197" t="s">
-        <v>6</v>
-      </c>
-      <c r="M197" t="s">
-        <v>6</v>
-      </c>
-      <c r="O197" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="198" spans="1:15">
@@ -7046,28 +7046,28 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
+        <v>403</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198" t="s">
         <v>404</v>
       </c>
-      <c r="C198">
-        <v>1</v>
-      </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>405</v>
       </c>
-      <c r="E198" t="s">
-        <v>406</v>
-      </c>
       <c r="F198" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G198">
         <v>39</v>
       </c>
       <c r="I198" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O198" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199" spans="1:15">
@@ -7075,28 +7075,28 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
+        <v>406</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199" t="s">
+        <v>404</v>
+      </c>
+      <c r="E199" t="s">
         <v>407</v>
       </c>
-      <c r="C199">
-        <v>1</v>
-      </c>
-      <c r="D199" t="s">
-        <v>405</v>
-      </c>
-      <c r="E199" t="s">
-        <v>408</v>
-      </c>
       <c r="F199" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G199">
         <v>30</v>
       </c>
       <c r="I199" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O199" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:15">
@@ -7104,28 +7104,28 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
+        <v>408</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200" t="s">
+        <v>404</v>
+      </c>
+      <c r="E200" t="s">
         <v>409</v>
       </c>
-      <c r="C200">
-        <v>1</v>
-      </c>
-      <c r="D200" t="s">
-        <v>405</v>
-      </c>
-      <c r="E200" t="s">
-        <v>410</v>
-      </c>
       <c r="F200" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G200">
         <v>15</v>
       </c>
       <c r="I200" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O200" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="201" spans="1:15">
@@ -7133,28 +7133,28 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
+        <v>410</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201" t="s">
+        <v>404</v>
+      </c>
+      <c r="E201" t="s">
         <v>411</v>
       </c>
-      <c r="C201">
-        <v>1</v>
-      </c>
-      <c r="D201" t="s">
-        <v>405</v>
-      </c>
-      <c r="E201" t="s">
-        <v>412</v>
-      </c>
       <c r="F201" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G201">
         <v>10</v>
       </c>
       <c r="I201" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O201" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="202" spans="1:15">
@@ -7162,28 +7162,28 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
+        <v>412</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="D202" t="s">
+        <v>399</v>
+      </c>
+      <c r="E202" t="s">
         <v>413</v>
       </c>
-      <c r="C202">
-        <v>1</v>
-      </c>
-      <c r="D202" t="s">
-        <v>400</v>
-      </c>
-      <c r="E202" t="s">
-        <v>414</v>
-      </c>
       <c r="F202" t="s">
+        <v>3</v>
+      </c>
+      <c r="G202">
+        <v>16</v>
+      </c>
+      <c r="I202" t="s">
         <v>4</v>
       </c>
-      <c r="G202">
-        <v>16</v>
-      </c>
-      <c r="I202" t="s">
-        <v>5</v>
-      </c>
       <c r="O202" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203" spans="1:15">
@@ -7191,16 +7191,16 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C203">
         <v>0</v>
       </c>
       <c r="D203" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="204" spans="1:15">
@@ -7208,28 +7208,28 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
+        <v>416</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>404</v>
+      </c>
+      <c r="E204" t="s">
         <v>417</v>
       </c>
-      <c r="C204">
-        <v>1</v>
-      </c>
-      <c r="D204" t="s">
-        <v>405</v>
-      </c>
-      <c r="E204" t="s">
-        <v>418</v>
-      </c>
       <c r="F204" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G204">
         <v>33</v>
       </c>
       <c r="I204" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O204" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205" spans="1:15">
@@ -7237,16 +7237,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C205">
         <v>0</v>
       </c>
       <c r="D205" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E205" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="206" spans="1:15">
@@ -7254,16 +7254,16 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C206">
         <v>0</v>
       </c>
       <c r="D206" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E206" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="207" spans="1:15">
@@ -7271,28 +7271,28 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
+        <v>421</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207" t="s">
+        <v>404</v>
+      </c>
+      <c r="E207" t="s">
         <v>422</v>
       </c>
-      <c r="C207">
-        <v>1</v>
-      </c>
-      <c r="D207" t="s">
-        <v>405</v>
-      </c>
-      <c r="E207" t="s">
-        <v>423</v>
-      </c>
       <c r="F207" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G207">
         <v>32</v>
       </c>
       <c r="I207" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O207" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208" spans="1:15">
@@ -7300,31 +7300,31 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
+        <v>423</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208" t="s">
+        <v>399</v>
+      </c>
+      <c r="E208" t="s">
         <v>424</v>
       </c>
-      <c r="C208">
-        <v>1</v>
-      </c>
-      <c r="D208" t="s">
-        <v>400</v>
-      </c>
-      <c r="E208" t="s">
-        <v>425</v>
-      </c>
       <c r="F208" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G208">
         <v>20</v>
       </c>
       <c r="I208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K208" t="s">
         <v>5</v>
       </c>
-      <c r="K208" t="s">
+      <c r="O208" t="s">
         <v>6</v>
-      </c>
-      <c r="O208" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:15">
@@ -7332,28 +7332,28 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
+        <v>425</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209" t="s">
+        <v>404</v>
+      </c>
+      <c r="E209" t="s">
         <v>426</v>
       </c>
-      <c r="C209">
-        <v>1</v>
-      </c>
-      <c r="D209" t="s">
-        <v>405</v>
-      </c>
-      <c r="E209" t="s">
-        <v>427</v>
-      </c>
       <c r="F209" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G209">
         <v>66</v>
       </c>
       <c r="I209" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O209" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210" spans="1:15">
@@ -7361,37 +7361,37 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
+        <v>427</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210" t="s">
+        <v>399</v>
+      </c>
+      <c r="E210" t="s">
         <v>428</v>
       </c>
-      <c r="C210">
-        <v>1</v>
-      </c>
-      <c r="D210" t="s">
-        <v>400</v>
-      </c>
-      <c r="E210" t="s">
-        <v>429</v>
-      </c>
       <c r="F210" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G210">
         <v>150</v>
       </c>
       <c r="I210" t="s">
+        <v>4</v>
+      </c>
+      <c r="J210" t="s">
         <v>5</v>
       </c>
-      <c r="J210" t="s">
-        <v>6</v>
-      </c>
       <c r="K210" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L210" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N210" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:15">
@@ -7399,16 +7399,16 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C211">
         <v>0</v>
       </c>
       <c r="D211" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E211" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="212" spans="1:15">
@@ -7416,16 +7416,16 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C212">
         <v>0</v>
       </c>
       <c r="D212" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E212" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="213" spans="1:15">
@@ -7433,16 +7433,16 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C213">
         <v>0</v>
       </c>
       <c r="D213" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E213" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="214" spans="1:15">
@@ -7450,28 +7450,28 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
+        <v>435</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="D214" t="s">
+        <v>404</v>
+      </c>
+      <c r="E214" t="s">
         <v>436</v>
       </c>
-      <c r="C214">
-        <v>1</v>
-      </c>
-      <c r="D214" t="s">
-        <v>405</v>
-      </c>
-      <c r="E214" t="s">
-        <v>437</v>
-      </c>
       <c r="F214" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G214">
         <v>6</v>
       </c>
       <c r="I214" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O214" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="215" spans="1:15">
@@ -7479,28 +7479,28 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
+        <v>437</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215" t="s">
+        <v>404</v>
+      </c>
+      <c r="E215" t="s">
         <v>438</v>
       </c>
-      <c r="C215">
-        <v>1</v>
-      </c>
-      <c r="D215" t="s">
-        <v>405</v>
-      </c>
-      <c r="E215" t="s">
-        <v>439</v>
-      </c>
       <c r="F215" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G215">
         <v>20</v>
       </c>
       <c r="I215" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O215" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="216" spans="1:15">
@@ -7508,28 +7508,28 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
+        <v>439</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216" t="s">
+        <v>404</v>
+      </c>
+      <c r="E216" t="s">
         <v>440</v>
       </c>
-      <c r="C216">
-        <v>1</v>
-      </c>
-      <c r="D216" t="s">
-        <v>405</v>
-      </c>
-      <c r="E216" t="s">
-        <v>441</v>
-      </c>
       <c r="F216" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G216">
         <v>13</v>
       </c>
       <c r="I216" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O216" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217" spans="1:15">
@@ -7537,28 +7537,28 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
+        <v>441</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+      <c r="D217" t="s">
+        <v>399</v>
+      </c>
+      <c r="E217" t="s">
         <v>442</v>
       </c>
-      <c r="C217">
-        <v>1</v>
-      </c>
-      <c r="D217" t="s">
-        <v>400</v>
-      </c>
-      <c r="E217" t="s">
-        <v>443</v>
-      </c>
       <c r="F217" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G217">
         <v>95</v>
       </c>
       <c r="I217" t="s">
+        <v>4</v>
+      </c>
+      <c r="K217" t="s">
         <v>5</v>
-      </c>
-      <c r="K217" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:15">
@@ -7566,19 +7566,19 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
+        <v>443</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218" t="s">
         <v>444</v>
       </c>
-      <c r="C218">
-        <v>1</v>
-      </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>445</v>
       </c>
-      <c r="E218" t="s">
-        <v>446</v>
-      </c>
       <c r="F218" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G218">
         <v>93</v>
@@ -7587,19 +7587,19 @@
         <v>10</v>
       </c>
       <c r="I218" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J218" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K218" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L218" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N218" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="219" spans="1:15">
@@ -7607,25 +7607,25 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
+        <v>446</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219" t="s">
+        <v>444</v>
+      </c>
+      <c r="E219" t="s">
         <v>447</v>
       </c>
-      <c r="C219">
-        <v>1</v>
-      </c>
-      <c r="D219" t="s">
-        <v>445</v>
-      </c>
-      <c r="E219" t="s">
-        <v>448</v>
-      </c>
       <c r="F219" t="s">
+        <v>3</v>
+      </c>
+      <c r="I219" t="s">
         <v>4</v>
       </c>
-      <c r="I219" t="s">
-        <v>5</v>
-      </c>
       <c r="O219" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="220" spans="1:15">
@@ -7633,25 +7633,25 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
+        <v>448</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220" t="s">
         <v>449</v>
       </c>
-      <c r="C220">
-        <v>1</v>
-      </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
         <v>450</v>
       </c>
-      <c r="E220" t="s">
-        <v>451</v>
-      </c>
       <c r="F220" t="s">
+        <v>3</v>
+      </c>
+      <c r="I220" t="s">
         <v>4</v>
       </c>
-      <c r="I220" t="s">
-        <v>5</v>
-      </c>
       <c r="O220" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="221" spans="1:15">
@@ -7659,16 +7659,16 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C221">
         <v>0</v>
       </c>
       <c r="D221" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E221" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="222" spans="1:15">
@@ -7676,28 +7676,28 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
+        <v>453</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222" t="s">
+        <v>444</v>
+      </c>
+      <c r="E222" t="s">
         <v>454</v>
       </c>
-      <c r="C222">
-        <v>1</v>
-      </c>
-      <c r="D222" t="s">
-        <v>445</v>
-      </c>
-      <c r="E222" t="s">
-        <v>455</v>
-      </c>
       <c r="F222" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G222">
         <v>40</v>
       </c>
       <c r="I222" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O222" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="223" spans="1:15">
@@ -7705,28 +7705,28 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
+        <v>455</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="s">
+        <v>444</v>
+      </c>
+      <c r="E223" t="s">
         <v>456</v>
       </c>
-      <c r="C223">
-        <v>1</v>
-      </c>
-      <c r="D223" t="s">
-        <v>445</v>
-      </c>
-      <c r="E223" t="s">
-        <v>457</v>
-      </c>
       <c r="F223" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G223">
         <v>54</v>
       </c>
       <c r="I223" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O223" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="224" spans="1:15">
@@ -7734,40 +7734,40 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
+        <v>457</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224" t="s">
+        <v>444</v>
+      </c>
+      <c r="E224" t="s">
         <v>458</v>
       </c>
-      <c r="C224">
-        <v>1</v>
-      </c>
-      <c r="D224" t="s">
-        <v>445</v>
-      </c>
-      <c r="E224" t="s">
-        <v>459</v>
-      </c>
       <c r="F224" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G224">
         <v>47</v>
       </c>
       <c r="I224" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J224" t="s">
+        <v>5</v>
+      </c>
+      <c r="K224" t="s">
+        <v>5</v>
+      </c>
+      <c r="L224" t="s">
+        <v>5</v>
+      </c>
+      <c r="N224" t="s">
+        <v>5</v>
+      </c>
+      <c r="O224" t="s">
         <v>6</v>
-      </c>
-      <c r="K224" t="s">
-        <v>6</v>
-      </c>
-      <c r="L224" t="s">
-        <v>6</v>
-      </c>
-      <c r="N224" t="s">
-        <v>6</v>
-      </c>
-      <c r="O224" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:15">
@@ -7775,28 +7775,28 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
+        <v>459</v>
+      </c>
+      <c r="C225">
+        <v>1</v>
+      </c>
+      <c r="D225" t="s">
+        <v>449</v>
+      </c>
+      <c r="E225" t="s">
         <v>460</v>
       </c>
-      <c r="C225">
-        <v>1</v>
-      </c>
-      <c r="D225" t="s">
-        <v>450</v>
-      </c>
-      <c r="E225" t="s">
-        <v>461</v>
-      </c>
       <c r="F225" t="s">
+        <v>3</v>
+      </c>
+      <c r="G225">
+        <v>30</v>
+      </c>
+      <c r="I225" t="s">
         <v>4</v>
       </c>
-      <c r="G225">
-        <v>30</v>
-      </c>
-      <c r="I225" t="s">
-        <v>5</v>
-      </c>
       <c r="O225" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="226" spans="1:15">
@@ -7804,19 +7804,19 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
+        <v>461</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
+        <v>444</v>
+      </c>
+      <c r="E226" t="s">
         <v>462</v>
       </c>
-      <c r="C226">
-        <v>1</v>
-      </c>
-      <c r="D226" t="s">
-        <v>445</v>
-      </c>
-      <c r="E226" t="s">
-        <v>463</v>
-      </c>
       <c r="F226" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G226">
         <v>300</v>
@@ -7825,19 +7825,19 @@
         <v>10</v>
       </c>
       <c r="I226" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J226" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K226" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L226" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N226" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="227" spans="1:15">
@@ -7845,19 +7845,19 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
+        <v>463</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227" t="s">
+        <v>444</v>
+      </c>
+      <c r="E227" t="s">
         <v>464</v>
       </c>
-      <c r="C227">
-        <v>1</v>
-      </c>
-      <c r="D227" t="s">
-        <v>445</v>
-      </c>
-      <c r="E227" t="s">
-        <v>465</v>
-      </c>
       <c r="F227" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G227">
         <v>42</v>
@@ -7866,10 +7866,10 @@
         <v>15</v>
       </c>
       <c r="I227" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K227" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:15">
@@ -7877,28 +7877,28 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
+        <v>465</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228" t="s">
+        <v>444</v>
+      </c>
+      <c r="E228" t="s">
         <v>466</v>
       </c>
-      <c r="C228">
-        <v>1</v>
-      </c>
-      <c r="D228" t="s">
-        <v>445</v>
-      </c>
-      <c r="E228" t="s">
-        <v>467</v>
-      </c>
       <c r="F228" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G228">
         <v>15</v>
       </c>
       <c r="I228" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O228" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:15">
@@ -7906,16 +7906,16 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
+        <v>467</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229" t="s">
+        <v>449</v>
+      </c>
+      <c r="E229" t="s">
         <v>468</v>
-      </c>
-      <c r="C229">
-        <v>1</v>
-      </c>
-      <c r="D229" t="s">
-        <v>450</v>
-      </c>
-      <c r="E229" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:15">
@@ -7923,28 +7923,28 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
+        <v>469</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="D230" t="s">
+        <v>444</v>
+      </c>
+      <c r="E230" t="s">
         <v>470</v>
       </c>
-      <c r="C230">
-        <v>1</v>
-      </c>
-      <c r="D230" t="s">
-        <v>445</v>
-      </c>
-      <c r="E230" t="s">
-        <v>471</v>
-      </c>
       <c r="F230" t="s">
+        <v>3</v>
+      </c>
+      <c r="G230">
+        <v>30</v>
+      </c>
+      <c r="I230" t="s">
         <v>4</v>
       </c>
-      <c r="G230">
-        <v>30</v>
-      </c>
-      <c r="I230" t="s">
-        <v>5</v>
-      </c>
       <c r="O230" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:15">
@@ -7952,16 +7952,16 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
+        <v>471</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231" t="s">
+        <v>449</v>
+      </c>
+      <c r="E231" t="s">
         <v>472</v>
-      </c>
-      <c r="C231">
-        <v>1</v>
-      </c>
-      <c r="D231" t="s">
-        <v>450</v>
-      </c>
-      <c r="E231" t="s">
-        <v>473</v>
       </c>
     </row>
   </sheetData>
